--- a/research/traditional_assets/database/data/namibia/namibia_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/namibia/namibia_telecom_wireless.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nmse_moc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,24 +589,54 @@
           <t>Telecom (Wireless)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="E2">
+        <v>0.022</v>
+      </c>
+      <c r="G2">
+        <v>0.4461633663366337</v>
+      </c>
+      <c r="H2">
+        <v>0.4461633663366337</v>
+      </c>
+      <c r="I2">
+        <v>0.3650809500150231</v>
+      </c>
+      <c r="J2">
+        <v>0.2576011183306003</v>
+      </c>
       <c r="K2">
-        <v>0</v>
+        <v>44.1</v>
+      </c>
+      <c r="L2">
+        <v>0.2728960396039604</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.09389213775178687</v>
+      </c>
+      <c r="O2">
+        <v>0.655328798185941</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.09389213775178687</v>
+      </c>
+      <c r="R2">
+        <v>0.655328798185941</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
         <v>0</v>
       </c>
@@ -612,55 +644,61 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.06944460242220553</v>
+        <v>0.1213654559949513</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2711.755742630081</v>
       </c>
       <c r="AA2">
-        <v>-0.1287248353386599</v>
+        <v>698.5513119409367</v>
       </c>
       <c r="AB2">
-        <v>0.0694009035054346</v>
+        <v>0.1213554390807386</v>
       </c>
       <c r="AC2">
-        <v>-0.1981257388440945</v>
+        <v>698.4299565018559</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.6734463571998643</v>
+        <v>0.05959238786132971</v>
       </c>
       <c r="AF2">
-        <v>0.6734463571998643</v>
+        <v>0.05959238786132971</v>
       </c>
       <c r="AG2">
-        <v>0.6734463571998643</v>
+        <v>0.05959238786132971</v>
       </c>
       <c r="AH2">
-        <v>0.001587293202018783</v>
+        <v>0.0001935700213175472</v>
       </c>
       <c r="AI2">
         <v>1</v>
       </c>
       <c r="AJ2">
-        <v>0.001587293202018783</v>
+        <v>0.0001935700213175472</v>
       </c>
       <c r="AK2">
         <v>1</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-3.51</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>47.2</v>
+      </c>
       <c r="AP2">
-        <v>14.03013244166384</v>
+        <v>0.0008264209441446935</v>
+      </c>
+      <c r="AQ2">
+        <v>-16.80911680911681</v>
       </c>
     </row>
     <row r="3">
@@ -679,24 +717,54 @@
           <t>Telecom (Wireless)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="E3">
+        <v>0.022</v>
+      </c>
+      <c r="G3">
+        <v>0.4461633663366337</v>
+      </c>
+      <c r="H3">
+        <v>0.4461633663366337</v>
+      </c>
+      <c r="I3">
+        <v>0.3650809500150231</v>
+      </c>
+      <c r="J3">
+        <v>0.2576011183306003</v>
+      </c>
       <c r="K3">
-        <v>0</v>
+        <v>44.1</v>
+      </c>
+      <c r="L3">
+        <v>0.2728960396039604</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>28.9</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.09389213775178687</v>
+      </c>
+      <c r="O3">
+        <v>0.655328798185941</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>28.9</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.09389213775178687</v>
+      </c>
+      <c r="R3">
+        <v>0.655328798185941</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
         <v>0</v>
       </c>
@@ -704,55 +772,8770 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.06944460242220553</v>
+        <v>0.1213654559949513</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2711.755742630081</v>
       </c>
       <c r="AA3">
-        <v>-0.1287248353386599</v>
+        <v>698.5513119409367</v>
       </c>
       <c r="AB3">
-        <v>0.0694009035054346</v>
+        <v>0.1213554390807386</v>
       </c>
       <c r="AC3">
-        <v>-0.1981257388440945</v>
+        <v>698.4299565018559</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.6734463571998643</v>
+        <v>0.05959238786132971</v>
       </c>
       <c r="AF3">
-        <v>0.6734463571998643</v>
+        <v>0.05959238786132971</v>
       </c>
       <c r="AG3">
-        <v>0.6734463571998643</v>
+        <v>0.05959238786132971</v>
       </c>
       <c r="AH3">
-        <v>0.001587293202018783</v>
+        <v>0.0001935700213175472</v>
       </c>
       <c r="AI3">
         <v>1</v>
       </c>
       <c r="AJ3">
-        <v>0.001587293202018783</v>
+        <v>0.0001935700213175472</v>
       </c>
       <c r="AK3">
         <v>1</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-3.51</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>47.2</v>
+      </c>
       <c r="AP3">
-        <v>14.03013244166384</v>
+        <v>0.0008264209441446935</v>
+      </c>
+      <c r="AQ3">
+        <v>-16.80911680911681</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mobile Telecommunications Limited (NMSE:MOC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NMSE:MOC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Telecom (Wireless)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.000193570021317547</v>
+      </c>
+      <c r="F2">
+        <v>0.64</v>
+      </c>
+      <c r="G2">
+        <v>307.8</v>
+      </c>
+      <c r="H2">
+        <v>167.376036711985</v>
+      </c>
+      <c r="I2">
+        <v>307.859592387861</v>
+      </c>
+      <c r="J2">
+        <v>364.406175840216</v>
+      </c>
+      <c r="K2">
+        <v>0.0595923878613297</v>
+      </c>
+      <c r="L2">
+        <v>197.030139128231</v>
+      </c>
+      <c r="M2">
+        <v>0.121355439080739</v>
+      </c>
+      <c r="N2">
+        <v>0.103551407922518</v>
+      </c>
+      <c r="O2">
+        <v>0.06961718348623849</v>
+      </c>
+      <c r="P2">
+        <v>0.0374</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.121365455994951</v>
+      </c>
+      <c r="T2">
+        <v>0.221153910895883</v>
+      </c>
+      <c r="U2">
+        <v>0.603385095061899</v>
+      </c>
+      <c r="V2">
+        <v>1.33263518665178</v>
+      </c>
+      <c r="W2">
+        <v>4.504064035902658</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>307.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.1368370824381754</v>
+      </c>
+      <c r="AC2">
+        <v>0.1023782110091743</v>
+      </c>
+      <c r="AD2">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="AH2">
+        <v>23.3</v>
+      </c>
+      <c r="AI2">
+        <v>21.4</v>
+      </c>
+      <c r="AJ2">
+        <v>0.05959238786132971</v>
+      </c>
+      <c r="AK2">
+        <v>-6.938893903907228e-18</v>
+      </c>
+      <c r="AL2">
+        <v>1.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1213545874277137</v>
+      </c>
+      <c r="C2">
+        <v>307.8618775704303</v>
+      </c>
+      <c r="D2">
+        <v>307.8618775704303</v>
+      </c>
+      <c r="E2">
+        <v>-0.05959238786132971</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>307.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K2">
+        <v>23.3</v>
+      </c>
+      <c r="L2">
+        <v>48.809</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>48.809</v>
+      </c>
+      <c r="O2">
+        <v>15.61888</v>
+      </c>
+      <c r="P2">
+        <v>33.19011999999999</v>
+      </c>
+      <c r="Q2">
+        <v>56.49011999999999</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1213545874277137</v>
+      </c>
+      <c r="T2">
+        <v>0.6033056680013098</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W2">
+        <v>0.031076</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.121013172747945</v>
+      </c>
+      <c r="C3">
+        <v>305.7021173787506</v>
+      </c>
+      <c r="D3">
+        <v>308.7807133026292</v>
+      </c>
+      <c r="E3">
+        <v>3.019003536017284</v>
+      </c>
+      <c r="F3">
+        <v>3.078595923878614</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>307.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K3">
+        <v>23.3</v>
+      </c>
+      <c r="L3">
+        <v>48.809</v>
+      </c>
+      <c r="M3">
+        <v>0.1406918337212527</v>
+      </c>
+      <c r="N3">
+        <v>48.66830816627874</v>
+      </c>
+      <c r="O3">
+        <v>15.5738586132092</v>
+      </c>
+      <c r="P3">
+        <v>33.09444955306954</v>
+      </c>
+      <c r="Q3">
+        <v>56.39444955306953</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1219216290383283</v>
+      </c>
+      <c r="T3">
+        <v>0.6074495857209148</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W3">
+        <v>0.031076</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>346.921343684406</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1206717580681763</v>
+      </c>
+      <c r="C4">
+        <v>303.5478582669958</v>
+      </c>
+      <c r="D4">
+        <v>309.705050114753</v>
+      </c>
+      <c r="E4">
+        <v>6.097599459895897</v>
+      </c>
+      <c r="F4">
+        <v>6.157191847757227</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>307.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K4">
+        <v>23.3</v>
+      </c>
+      <c r="L4">
+        <v>48.809</v>
+      </c>
+      <c r="M4">
+        <v>0.2813836674425053</v>
+      </c>
+      <c r="N4">
+        <v>48.52761633255749</v>
+      </c>
+      <c r="O4">
+        <v>15.5288372264184</v>
+      </c>
+      <c r="P4">
+        <v>32.9987791061391</v>
+      </c>
+      <c r="Q4">
+        <v>56.29877910613909</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1225002429267105</v>
+      </c>
+      <c r="T4">
+        <v>0.6116780731898994</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W4">
+        <v>0.031076</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>173.460671842203</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1203303433884076</v>
+      </c>
+      <c r="C5">
+        <v>301.3991497860384</v>
+      </c>
+      <c r="D5">
+        <v>310.6349375576742</v>
+      </c>
+      <c r="E5">
+        <v>9.176195383774511</v>
+      </c>
+      <c r="F5">
+        <v>9.23578777163584</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>307.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K5">
+        <v>23.3</v>
+      </c>
+      <c r="L5">
+        <v>48.809</v>
+      </c>
+      <c r="M5">
+        <v>0.4220755011637579</v>
+      </c>
+      <c r="N5">
+        <v>48.38692449883624</v>
+      </c>
+      <c r="O5">
+        <v>15.4838158396276</v>
+      </c>
+      <c r="P5">
+        <v>32.90310865920864</v>
+      </c>
+      <c r="Q5">
+        <v>56.20310865920864</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1230907869983584</v>
+      </c>
+      <c r="T5">
+        <v>0.6159937459675229</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W5">
+        <v>0.031076</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>115.640447894802</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.119988928708639</v>
+      </c>
+      <c r="C6">
+        <v>299.2560420836475</v>
+      </c>
+      <c r="D6">
+        <v>311.570425779162</v>
+      </c>
+      <c r="E6">
+        <v>12.25479130765313</v>
+      </c>
+      <c r="F6">
+        <v>12.31438369551445</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>307.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K6">
+        <v>23.3</v>
+      </c>
+      <c r="L6">
+        <v>48.809</v>
+      </c>
+      <c r="M6">
+        <v>0.5627673348850106</v>
+      </c>
+      <c r="N6">
+        <v>48.24623266511499</v>
+      </c>
+      <c r="O6">
+        <v>15.4387944528368</v>
+      </c>
+      <c r="P6">
+        <v>32.80743821227819</v>
+      </c>
+      <c r="Q6">
+        <v>56.10743821227818</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1236936340714989</v>
+      </c>
+      <c r="T6">
+        <v>0.6203993285946803</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W6">
+        <v>0.031076</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>86.73033592110151</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1196475140288703</v>
+      </c>
+      <c r="C7">
+        <v>297.1185859135046</v>
+      </c>
+      <c r="D7">
+        <v>312.5115655328977</v>
+      </c>
+      <c r="E7">
+        <v>15.33338723153174</v>
+      </c>
+      <c r="F7">
+        <v>15.39297961939307</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>307.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K7">
+        <v>23.3</v>
+      </c>
+      <c r="L7">
+        <v>48.809</v>
+      </c>
+      <c r="M7">
+        <v>0.7034591686062633</v>
+      </c>
+      <c r="N7">
+        <v>48.10554083139373</v>
+      </c>
+      <c r="O7">
+        <v>15.393773066046</v>
+      </c>
+      <c r="P7">
+        <v>32.71176776534774</v>
+      </c>
+      <c r="Q7">
+        <v>56.01176776534774</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1243091726619687</v>
+      </c>
+      <c r="T7">
+        <v>0.6248976603297778</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W7">
+        <v>0.031076</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>69.3842687368812</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1193060993491016</v>
+      </c>
+      <c r="C8">
+        <v>294.9868326443816</v>
+      </c>
+      <c r="D8">
+        <v>313.4584081876533</v>
+      </c>
+      <c r="E8">
+        <v>18.41198315541035</v>
+      </c>
+      <c r="F8">
+        <v>18.47157554327168</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>307.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K8">
+        <v>23.3</v>
+      </c>
+      <c r="L8">
+        <v>48.809</v>
+      </c>
+      <c r="M8">
+        <v>0.8441510023275158</v>
+      </c>
+      <c r="N8">
+        <v>47.96484899767248</v>
+      </c>
+      <c r="O8">
+        <v>15.3487516792552</v>
+      </c>
+      <c r="P8">
+        <v>32.61609731841729</v>
+      </c>
+      <c r="Q8">
+        <v>55.91609731841729</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1249378078181932</v>
+      </c>
+      <c r="T8">
+        <v>0.6294917012507284</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W8">
+        <v>0.031076</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>57.82022394740101</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1189646846693329</v>
+      </c>
+      <c r="C9">
+        <v>292.8608342694881</v>
+      </c>
+      <c r="D9">
+        <v>314.4110057366384</v>
+      </c>
+      <c r="E9">
+        <v>21.49057907928897</v>
+      </c>
+      <c r="F9">
+        <v>21.5501714671503</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>307.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K9">
+        <v>23.3</v>
+      </c>
+      <c r="L9">
+        <v>48.809</v>
+      </c>
+      <c r="M9">
+        <v>0.9848428360487688</v>
+      </c>
+      <c r="N9">
+        <v>47.82415716395123</v>
+      </c>
+      <c r="O9">
+        <v>15.3037302924644</v>
+      </c>
+      <c r="P9">
+        <v>32.52042687148683</v>
+      </c>
+      <c r="Q9">
+        <v>55.82042687148683</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1255799620100354</v>
+      </c>
+      <c r="T9">
+        <v>0.6341845387506242</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W9">
+        <v>0.031076</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>49.56019195491513</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1186232699895642</v>
+      </c>
+      <c r="C10">
+        <v>290.7406434159872</v>
+      </c>
+      <c r="D10">
+        <v>315.3694108070162</v>
+      </c>
+      <c r="E10">
+        <v>24.56917500316758</v>
+      </c>
+      <c r="F10">
+        <v>24.62876739102891</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>307.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K10">
+        <v>23.3</v>
+      </c>
+      <c r="L10">
+        <v>48.809</v>
+      </c>
+      <c r="M10">
+        <v>1.125534669770021</v>
+      </c>
+      <c r="N10">
+        <v>47.68346533022998</v>
+      </c>
+      <c r="O10">
+        <v>15.2587089056736</v>
+      </c>
+      <c r="P10">
+        <v>32.42475642455638</v>
+      </c>
+      <c r="Q10">
+        <v>55.72475642455638</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1262360760756133</v>
+      </c>
+      <c r="T10">
+        <v>0.6389793944570394</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W10">
+        <v>0.031076</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>43.36516796055076</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1182818553097955</v>
+      </c>
+      <c r="C11">
+        <v>288.626313354689</v>
+      </c>
+      <c r="D11">
+        <v>316.3336766695965</v>
+      </c>
+      <c r="E11">
+        <v>27.64777092704619</v>
+      </c>
+      <c r="F11">
+        <v>27.70736331490752</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>307.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K11">
+        <v>23.3</v>
+      </c>
+      <c r="L11">
+        <v>48.809</v>
+      </c>
+      <c r="M11">
+        <v>1.266226503491274</v>
+      </c>
+      <c r="N11">
+        <v>47.54277349650872</v>
+      </c>
+      <c r="O11">
+        <v>15.21368751888279</v>
+      </c>
+      <c r="P11">
+        <v>32.32908597762593</v>
+      </c>
+      <c r="Q11">
+        <v>55.62908597762593</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1269066102305446</v>
+      </c>
+      <c r="T11">
+        <v>0.6438796316075518</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W11">
+        <v>0.031076</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>38.54681596493401</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1179404406300269</v>
+      </c>
+      <c r="C12">
+        <v>286.5178980099192</v>
+      </c>
+      <c r="D12">
+        <v>317.3038572487054</v>
+      </c>
+      <c r="E12">
+        <v>30.72636685092481</v>
+      </c>
+      <c r="F12">
+        <v>30.78595923878614</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>307.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K12">
+        <v>23.3</v>
+      </c>
+      <c r="L12">
+        <v>48.809</v>
+      </c>
+      <c r="M12">
+        <v>1.406918337212527</v>
+      </c>
+      <c r="N12">
+        <v>47.40208166278747</v>
+      </c>
+      <c r="O12">
+        <v>15.16866613209199</v>
+      </c>
+      <c r="P12">
+        <v>32.23341553069548</v>
+      </c>
+      <c r="Q12">
+        <v>55.53341553069548</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1275920451444743</v>
+      </c>
+      <c r="T12">
+        <v>0.6488887629169644</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W12">
+        <v>0.031076</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>34.6921343684406</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1175990259502582</v>
+      </c>
+      <c r="C13">
+        <v>284.4154519695728</v>
+      </c>
+      <c r="D13">
+        <v>318.2800071322376</v>
+      </c>
+      <c r="E13">
+        <v>33.80496277480342</v>
+      </c>
+      <c r="F13">
+        <v>33.86455516266475</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>307.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K13">
+        <v>23.3</v>
+      </c>
+      <c r="L13">
+        <v>48.809</v>
+      </c>
+      <c r="M13">
+        <v>1.547610170933779</v>
+      </c>
+      <c r="N13">
+        <v>47.26138982906622</v>
+      </c>
+      <c r="O13">
+        <v>15.12364474530119</v>
+      </c>
+      <c r="P13">
+        <v>32.13774508376503</v>
+      </c>
+      <c r="Q13">
+        <v>55.43774508376502</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1282928830901777</v>
+      </c>
+      <c r="T13">
+        <v>0.654010458974903</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W13">
+        <v>0.031076</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>31.53830397130964</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1172576112704895</v>
+      </c>
+      <c r="C14">
+        <v>282.3190304953516</v>
+      </c>
+      <c r="D14">
+        <v>319.2621815818949</v>
+      </c>
+      <c r="E14">
+        <v>36.88355869868203</v>
+      </c>
+      <c r="F14">
+        <v>36.94315108654336</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>307.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K14">
+        <v>23.3</v>
+      </c>
+      <c r="L14">
+        <v>48.809</v>
+      </c>
+      <c r="M14">
+        <v>1.688302004655032</v>
+      </c>
+      <c r="N14">
+        <v>47.12069799534497</v>
+      </c>
+      <c r="O14">
+        <v>15.07862335851039</v>
+      </c>
+      <c r="P14">
+        <v>32.04207463683458</v>
+      </c>
+      <c r="Q14">
+        <v>55.34207463683458</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1290096491710108</v>
+      </c>
+      <c r="T14">
+        <v>0.6592485572159767</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W14">
+        <v>0.031076</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>28.91011197370051</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1169161965907208</v>
+      </c>
+      <c r="C15">
+        <v>280.2286895331932</v>
+      </c>
+      <c r="D15">
+        <v>320.2504365436151</v>
+      </c>
+      <c r="E15">
+        <v>39.96215462256065</v>
+      </c>
+      <c r="F15">
+        <v>40.02174701042198</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>307.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K15">
+        <v>23.3</v>
+      </c>
+      <c r="L15">
+        <v>48.809</v>
+      </c>
+      <c r="M15">
+        <v>1.828993838376285</v>
+      </c>
+      <c r="N15">
+        <v>46.98000616162371</v>
+      </c>
+      <c r="O15">
+        <v>15.03360197171959</v>
+      </c>
+      <c r="P15">
+        <v>31.94640418990412</v>
+      </c>
+      <c r="Q15">
+        <v>55.24640418990413</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1297428926330124</v>
+      </c>
+      <c r="T15">
+        <v>0.6646070715085693</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W15">
+        <v>0.031076</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>26.68625720649277</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1165747819109521</v>
+      </c>
+      <c r="C16">
+        <v>278.1444857238937</v>
+      </c>
+      <c r="D16">
+        <v>321.2448286581943</v>
+      </c>
+      <c r="E16">
+        <v>43.04075054643927</v>
+      </c>
+      <c r="F16">
+        <v>43.1003429343006</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>307.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K16">
+        <v>23.3</v>
+      </c>
+      <c r="L16">
+        <v>48.809</v>
+      </c>
+      <c r="M16">
+        <v>1.969685672097538</v>
+      </c>
+      <c r="N16">
+        <v>46.83931432790246</v>
+      </c>
+      <c r="O16">
+        <v>14.98858058492879</v>
+      </c>
+      <c r="P16">
+        <v>31.85073374297367</v>
+      </c>
+      <c r="Q16">
+        <v>55.15073374297367</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.130493188268549</v>
+      </c>
+      <c r="T16">
+        <v>0.6700902024126175</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W16">
+        <v>0.031076</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>24.78009597745757</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1162333672311834</v>
+      </c>
+      <c r="C17">
+        <v>276.0664764139299</v>
+      </c>
+      <c r="D17">
+        <v>322.2454152721091</v>
+      </c>
+      <c r="E17">
+        <v>46.11934647031787</v>
+      </c>
+      <c r="F17">
+        <v>46.1789388581792</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>307.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K17">
+        <v>23.3</v>
+      </c>
+      <c r="L17">
+        <v>48.809</v>
+      </c>
+      <c r="M17">
+        <v>2.11037750581879</v>
+      </c>
+      <c r="N17">
+        <v>46.69862249418121</v>
+      </c>
+      <c r="O17">
+        <v>14.94355919813799</v>
+      </c>
+      <c r="P17">
+        <v>31.75506329604322</v>
+      </c>
+      <c r="Q17">
+        <v>55.05506329604322</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1312611379190393</v>
+      </c>
+      <c r="T17">
+        <v>0.675702348161467</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W17">
+        <v>0.031076</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>23.1280895789604</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1158919525514148</v>
+      </c>
+      <c r="C18">
+        <v>273.9947196664825</v>
+      </c>
+      <c r="D18">
+        <v>323.2522544485403</v>
+      </c>
+      <c r="E18">
+        <v>49.19794239419649</v>
+      </c>
+      <c r="F18">
+        <v>49.25753478205782</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>307.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K18">
+        <v>23.3</v>
+      </c>
+      <c r="L18">
+        <v>48.809</v>
+      </c>
+      <c r="M18">
+        <v>2.251069339540043</v>
+      </c>
+      <c r="N18">
+        <v>46.55793066045995</v>
+      </c>
+      <c r="O18">
+        <v>14.89853781134719</v>
+      </c>
+      <c r="P18">
+        <v>31.65939284911276</v>
+      </c>
+      <c r="Q18">
+        <v>54.95939284911276</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1320473720850176</v>
+      </c>
+      <c r="T18">
+        <v>0.6814481164281462</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W18">
+        <v>0.031076</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>21.68258398027537</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1155505378716461</v>
+      </c>
+      <c r="C19">
+        <v>271.9292742726682</v>
+      </c>
+      <c r="D19">
+        <v>324.2654049786046</v>
+      </c>
+      <c r="E19">
+        <v>52.2765383180751</v>
+      </c>
+      <c r="F19">
+        <v>52.33613070593643</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>307.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K19">
+        <v>23.3</v>
+      </c>
+      <c r="L19">
+        <v>48.809</v>
+      </c>
+      <c r="M19">
+        <v>2.391761173261295</v>
+      </c>
+      <c r="N19">
+        <v>46.4172388267387</v>
+      </c>
+      <c r="O19">
+        <v>14.85351642455639</v>
+      </c>
+      <c r="P19">
+        <v>31.56372240218231</v>
+      </c>
+      <c r="Q19">
+        <v>54.86372240218232</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1328525516525856</v>
+      </c>
+      <c r="T19">
+        <v>0.6873323369422152</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W19">
+        <v>0.031076</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>20.40713786378859</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1152091231918774</v>
+      </c>
+      <c r="C20">
+        <v>269.8701997629837</v>
+      </c>
+      <c r="D20">
+        <v>325.2849263927988</v>
+      </c>
+      <c r="E20">
+        <v>55.35513424195371</v>
+      </c>
+      <c r="F20">
+        <v>55.41472662981504</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>307.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K20">
+        <v>23.3</v>
+      </c>
+      <c r="L20">
+        <v>48.809</v>
+      </c>
+      <c r="M20">
+        <v>2.532453006982548</v>
+      </c>
+      <c r="N20">
+        <v>46.27654699301745</v>
+      </c>
+      <c r="O20">
+        <v>14.80849503776559</v>
+      </c>
+      <c r="P20">
+        <v>31.46805195525186</v>
+      </c>
+      <c r="Q20">
+        <v>54.76805195525186</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1336773697461919</v>
+      </c>
+      <c r="T20">
+        <v>0.6933600750297979</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W20">
+        <v>0.031076</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>19.273407982467</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1148677085121087</v>
+      </c>
+      <c r="C21">
+        <v>267.8175564189651</v>
+      </c>
+      <c r="D21">
+        <v>326.3108789726588</v>
+      </c>
+      <c r="E21">
+        <v>58.43373016583233</v>
+      </c>
+      <c r="F21">
+        <v>58.49332255369366</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>307.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K21">
+        <v>23.3</v>
+      </c>
+      <c r="L21">
+        <v>48.809</v>
+      </c>
+      <c r="M21">
+        <v>2.673144840703801</v>
+      </c>
+      <c r="N21">
+        <v>46.1358551592962</v>
+      </c>
+      <c r="O21">
+        <v>14.76347365097479</v>
+      </c>
+      <c r="P21">
+        <v>31.37238150832141</v>
+      </c>
+      <c r="Q21">
+        <v>54.67238150832141</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1345225537186527</v>
+      </c>
+      <c r="T21">
+        <v>0.6995366461565805</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W21">
+        <v>0.031076</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>18.25901808865295</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.11452629383234</v>
+      </c>
+      <c r="C22">
+        <v>265.7714052850694</v>
+      </c>
+      <c r="D22">
+        <v>327.3433237626417</v>
+      </c>
+      <c r="E22">
+        <v>61.51232608971095</v>
+      </c>
+      <c r="F22">
+        <v>61.57191847757228</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>307.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K22">
+        <v>23.3</v>
+      </c>
+      <c r="L22">
+        <v>48.809</v>
+      </c>
+      <c r="M22">
+        <v>2.813836674425053</v>
+      </c>
+      <c r="N22">
+        <v>45.99516332557494</v>
+      </c>
+      <c r="O22">
+        <v>14.71845226418398</v>
+      </c>
+      <c r="P22">
+        <v>31.27671106139096</v>
+      </c>
+      <c r="Q22">
+        <v>54.57671106139096</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.135388867290425</v>
+      </c>
+      <c r="T22">
+        <v>0.7058676315615324</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W22">
+        <v>0.031076</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>17.3460671842203</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1141848791525713</v>
+      </c>
+      <c r="C23">
+        <v>263.7318081807825</v>
+      </c>
+      <c r="D23">
+        <v>328.3823225822334</v>
+      </c>
+      <c r="E23">
+        <v>64.59092201358956</v>
+      </c>
+      <c r="F23">
+        <v>64.65051440145089</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>307.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K23">
+        <v>23.3</v>
+      </c>
+      <c r="L23">
+        <v>48.809</v>
+      </c>
+      <c r="M23">
+        <v>2.954528508146306</v>
+      </c>
+      <c r="N23">
+        <v>45.85447149185369</v>
+      </c>
+      <c r="O23">
+        <v>14.67343087739319</v>
+      </c>
+      <c r="P23">
+        <v>31.18104061446051</v>
+      </c>
+      <c r="Q23">
+        <v>54.48104061446051</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1362771128513561</v>
+      </c>
+      <c r="T23">
+        <v>0.7123588950780022</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W23">
+        <v>0.031076</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>16.52006398497171</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1138434644728027</v>
+      </c>
+      <c r="C24">
+        <v>261.6988277129578</v>
+      </c>
+      <c r="D24">
+        <v>329.4279380382873</v>
+      </c>
+      <c r="E24">
+        <v>67.66951793746817</v>
+      </c>
+      <c r="F24">
+        <v>67.7291103253295</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>307.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K24">
+        <v>23.3</v>
+      </c>
+      <c r="L24">
+        <v>48.809</v>
+      </c>
+      <c r="M24">
+        <v>3.095220341867559</v>
+      </c>
+      <c r="N24">
+        <v>45.71377965813244</v>
+      </c>
+      <c r="O24">
+        <v>14.62840949060238</v>
+      </c>
+      <c r="P24">
+        <v>31.08537016753005</v>
+      </c>
+      <c r="Q24">
+        <v>54.38537016753006</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1371881339394906</v>
+      </c>
+      <c r="T24">
+        <v>0.7190166012487406</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W24">
+        <v>0.031076</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>15.76915198565482</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.113502049793034</v>
+      </c>
+      <c r="C25">
+        <v>259.6725272883923</v>
+      </c>
+      <c r="D25">
+        <v>330.4802335376004</v>
+      </c>
+      <c r="E25">
+        <v>70.74811386134679</v>
+      </c>
+      <c r="F25">
+        <v>70.80770624920812</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>307.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K25">
+        <v>23.3</v>
+      </c>
+      <c r="L25">
+        <v>48.809</v>
+      </c>
+      <c r="M25">
+        <v>3.235912175588811</v>
+      </c>
+      <c r="N25">
+        <v>45.57308782441119</v>
+      </c>
+      <c r="O25">
+        <v>14.58338810381158</v>
+      </c>
+      <c r="P25">
+        <v>30.98969972059961</v>
+      </c>
+      <c r="Q25">
+        <v>54.28969972059961</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1381228179130311</v>
+      </c>
+      <c r="T25">
+        <v>0.7258472348524849</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W25">
+        <v>0.031076</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>15.0835366819307</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1131606351132653</v>
+      </c>
+      <c r="C26">
+        <v>257.652971126643</v>
+      </c>
+      <c r="D26">
+        <v>331.5392732997298</v>
+      </c>
+      <c r="E26">
+        <v>73.82670978522539</v>
+      </c>
+      <c r="F26">
+        <v>73.88630217308672</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>307.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K26">
+        <v>23.3</v>
+      </c>
+      <c r="L26">
+        <v>48.809</v>
+      </c>
+      <c r="M26">
+        <v>3.376604009310063</v>
+      </c>
+      <c r="N26">
+        <v>45.43239599068993</v>
+      </c>
+      <c r="O26">
+        <v>14.53836671702078</v>
+      </c>
+      <c r="P26">
+        <v>30.89402927366915</v>
+      </c>
+      <c r="Q26">
+        <v>54.19402927366915</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1390820988332438</v>
+      </c>
+      <c r="T26">
+        <v>0.7328576219721173</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W26">
+        <v>0.031076</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>14.45505598685025</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1128192204334966</v>
+      </c>
+      <c r="C27">
+        <v>255.6402242730924</v>
+      </c>
+      <c r="D27">
+        <v>332.6051223700577</v>
+      </c>
+      <c r="E27">
+        <v>76.90530570910401</v>
+      </c>
+      <c r="F27">
+        <v>76.96489809696534</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>307.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K27">
+        <v>23.3</v>
+      </c>
+      <c r="L27">
+        <v>48.809</v>
+      </c>
+      <c r="M27">
+        <v>3.517295843031317</v>
+      </c>
+      <c r="N27">
+        <v>45.29170415696868</v>
+      </c>
+      <c r="O27">
+        <v>14.49334533022998</v>
+      </c>
+      <c r="P27">
+        <v>30.7983588267387</v>
+      </c>
+      <c r="Q27">
+        <v>54.0983588267387</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1400669605779954</v>
+      </c>
+      <c r="T27">
+        <v>0.7400549527482733</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W27">
+        <v>0.031076</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>13.87685374737624</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1124778057537279</v>
+      </c>
+      <c r="C28">
+        <v>253.6343526122645</v>
+      </c>
+      <c r="D28">
+        <v>333.6778466331085</v>
+      </c>
+      <c r="E28">
+        <v>79.98390163298264</v>
+      </c>
+      <c r="F28">
+        <v>80.04349402084397</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>307.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K28">
+        <v>23.3</v>
+      </c>
+      <c r="L28">
+        <v>48.809</v>
+      </c>
+      <c r="M28">
+        <v>3.657987676752569</v>
+      </c>
+      <c r="N28">
+        <v>45.15101232324743</v>
+      </c>
+      <c r="O28">
+        <v>14.44832394343918</v>
+      </c>
+      <c r="P28">
+        <v>30.70268837980825</v>
+      </c>
+      <c r="Q28">
+        <v>54.00268837980825</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1410784402077404</v>
+      </c>
+      <c r="T28">
+        <v>0.747446805977839</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W28">
+        <v>0.031076</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>13.34312860324638</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1124301510739592</v>
+      </c>
+      <c r="C29">
+        <v>250.7060381680706</v>
+      </c>
+      <c r="D29">
+        <v>333.8281281127931</v>
+      </c>
+      <c r="E29">
+        <v>83.06249755686125</v>
+      </c>
+      <c r="F29">
+        <v>83.12208994472257</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>307.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K29">
+        <v>23.3</v>
+      </c>
+      <c r="L29">
+        <v>48.809</v>
+      </c>
+      <c r="M29">
+        <v>3.931674854385378</v>
+      </c>
+      <c r="N29">
+        <v>44.87732514561462</v>
+      </c>
+      <c r="O29">
+        <v>14.36074404659668</v>
+      </c>
+      <c r="P29">
+        <v>30.51658109901794</v>
+      </c>
+      <c r="Q29">
+        <v>53.81658109901794</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1421176316081633</v>
+      </c>
+      <c r="T29">
+        <v>0.755041175734242</v>
+      </c>
+      <c r="U29">
+        <v>0.0473</v>
+      </c>
+      <c r="V29">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W29">
+        <v>0.032164</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>12.41430225227261</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1120996163941906</v>
+      </c>
+      <c r="C30">
+        <v>248.6735376262037</v>
+      </c>
+      <c r="D30">
+        <v>334.8742234948049</v>
+      </c>
+      <c r="E30">
+        <v>86.14109348073987</v>
+      </c>
+      <c r="F30">
+        <v>86.2006858686012</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>307.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K30">
+        <v>23.3</v>
+      </c>
+      <c r="L30">
+        <v>48.809</v>
+      </c>
+      <c r="M30">
+        <v>4.077292441584837</v>
+      </c>
+      <c r="N30">
+        <v>44.73170755841516</v>
+      </c>
+      <c r="O30">
+        <v>14.31414641869285</v>
+      </c>
+      <c r="P30">
+        <v>30.41756113972231</v>
+      </c>
+      <c r="Q30">
+        <v>53.71756113972231</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1431856894363758</v>
+      </c>
+      <c r="T30">
+        <v>0.7628465002061007</v>
+      </c>
+      <c r="U30">
+        <v>0.0473</v>
+      </c>
+      <c r="V30">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W30">
+        <v>0.032164</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>11.97093431469145</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1117690817144218</v>
+      </c>
+      <c r="C31">
+        <v>246.6476138549594</v>
+      </c>
+      <c r="D31">
+        <v>335.9268956474392</v>
+      </c>
+      <c r="E31">
+        <v>89.21968940461846</v>
+      </c>
+      <c r="F31">
+        <v>89.27928179247979</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>307.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K31">
+        <v>23.3</v>
+      </c>
+      <c r="L31">
+        <v>48.809</v>
+      </c>
+      <c r="M31">
+        <v>4.222910028784295</v>
+      </c>
+      <c r="N31">
+        <v>44.5860899712157</v>
+      </c>
+      <c r="O31">
+        <v>14.26754879078903</v>
+      </c>
+      <c r="P31">
+        <v>30.31854118042667</v>
+      </c>
+      <c r="Q31">
+        <v>53.61854118042667</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1442838334005942</v>
+      </c>
+      <c r="T31">
+        <v>0.7708716929729411</v>
+      </c>
+      <c r="U31">
+        <v>0.0473</v>
+      </c>
+      <c r="V31">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W31">
+        <v>0.032164</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>11.55814347625381</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1114385470346532</v>
+      </c>
+      <c r="C32">
+        <v>244.6283290718598</v>
+      </c>
+      <c r="D32">
+        <v>336.9862067882182</v>
+      </c>
+      <c r="E32">
+        <v>92.29828532849707</v>
+      </c>
+      <c r="F32">
+        <v>92.3578777163584</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>307.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K32">
+        <v>23.3</v>
+      </c>
+      <c r="L32">
+        <v>48.809</v>
+      </c>
+      <c r="M32">
+        <v>4.368527615983752</v>
+      </c>
+      <c r="N32">
+        <v>44.44047238401625</v>
+      </c>
+      <c r="O32">
+        <v>14.2209511628852</v>
+      </c>
+      <c r="P32">
+        <v>30.21952122113105</v>
+      </c>
+      <c r="Q32">
+        <v>53.51952122113104</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1454133529066474</v>
+      </c>
+      <c r="T32">
+        <v>0.7791261769616915</v>
+      </c>
+      <c r="U32">
+        <v>0.0473</v>
+      </c>
+      <c r="V32">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W32">
+        <v>0.032164</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>11.17287202704535</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1111080123548845</v>
+      </c>
+      <c r="C33">
+        <v>242.6157462816965</v>
+      </c>
+      <c r="D33">
+        <v>338.0522199219336</v>
+      </c>
+      <c r="E33">
+        <v>95.3768812523757</v>
+      </c>
+      <c r="F33">
+        <v>95.43647364023703</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>307.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K33">
+        <v>23.3</v>
+      </c>
+      <c r="L33">
+        <v>48.809</v>
+      </c>
+      <c r="M33">
+        <v>4.514145203183212</v>
+      </c>
+      <c r="N33">
+        <v>44.29485479681679</v>
+      </c>
+      <c r="O33">
+        <v>14.17435353498137</v>
+      </c>
+      <c r="P33">
+        <v>30.12050126183541</v>
+      </c>
+      <c r="Q33">
+        <v>53.42050126183541</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1465756121085283</v>
+      </c>
+      <c r="T33">
+        <v>0.7876199213559129</v>
+      </c>
+      <c r="U33">
+        <v>0.0473</v>
+      </c>
+      <c r="V33">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W33">
+        <v>0.032164</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>10.81245680036647</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1107774776751158</v>
+      </c>
+      <c r="C34">
+        <v>240.6099292890216</v>
+      </c>
+      <c r="D34">
+        <v>339.1249988531372</v>
+      </c>
+      <c r="E34">
+        <v>98.45547717625431</v>
+      </c>
+      <c r="F34">
+        <v>98.51506956411563</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>307.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K34">
+        <v>23.3</v>
+      </c>
+      <c r="L34">
+        <v>48.809</v>
+      </c>
+      <c r="M34">
+        <v>4.659762790382669</v>
+      </c>
+      <c r="N34">
+        <v>44.14923720961733</v>
+      </c>
+      <c r="O34">
+        <v>14.12775590707755</v>
+      </c>
+      <c r="P34">
+        <v>30.02148130253978</v>
+      </c>
+      <c r="Q34">
+        <v>53.32148130253978</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1477720554045821</v>
+      </c>
+      <c r="T34">
+        <v>0.796363481761729</v>
+      </c>
+      <c r="U34">
+        <v>0.0473</v>
+      </c>
+      <c r="V34">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W34">
+        <v>0.032164</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>10.47456752535502</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1112996629953471</v>
+      </c>
+      <c r="C35">
+        <v>235.8396385662699</v>
+      </c>
+      <c r="D35">
+        <v>337.4333040542641</v>
+      </c>
+      <c r="E35">
+        <v>101.5340731001329</v>
+      </c>
+      <c r="F35">
+        <v>101.5936654879943</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>307.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K35">
+        <v>23.3</v>
+      </c>
+      <c r="L35">
+        <v>48.809</v>
+      </c>
+      <c r="M35">
+        <v>5.191436306436507</v>
+      </c>
+      <c r="N35">
+        <v>43.61756369356349</v>
+      </c>
+      <c r="O35">
+        <v>13.95762038194032</v>
+      </c>
+      <c r="P35">
+        <v>29.65994331162317</v>
+      </c>
+      <c r="Q35">
+        <v>52.95994331162317</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1490042134258913</v>
+      </c>
+      <c r="T35">
+        <v>0.8053680439707038</v>
+      </c>
+      <c r="U35">
+        <v>0.0511</v>
+      </c>
+      <c r="V35">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W35">
+        <v>0.03474799999999999</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>9.401829690077301</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1109949683155785</v>
+      </c>
+      <c r="C36">
+        <v>233.7460882173762</v>
+      </c>
+      <c r="D36">
+        <v>338.4183496292491</v>
+      </c>
+      <c r="E36">
+        <v>104.6126690240115</v>
+      </c>
+      <c r="F36">
+        <v>104.6722614118729</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>307.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K36">
+        <v>23.3</v>
+      </c>
+      <c r="L36">
+        <v>48.809</v>
+      </c>
+      <c r="M36">
+        <v>5.348752558146703</v>
+      </c>
+      <c r="N36">
+        <v>43.4602474418533</v>
+      </c>
+      <c r="O36">
+        <v>13.90727918139306</v>
+      </c>
+      <c r="P36">
+        <v>29.55296826046024</v>
+      </c>
+      <c r="Q36">
+        <v>52.85296826046024</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1502737095690583</v>
+      </c>
+      <c r="T36">
+        <v>0.8146454717011626</v>
+      </c>
+      <c r="U36">
+        <v>0.0511</v>
+      </c>
+      <c r="V36">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W36">
+        <v>0.03474799999999999</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>9.125305287427972</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1106902736358098</v>
+      </c>
+      <c r="C37">
+        <v>231.6583058566373</v>
+      </c>
+      <c r="D37">
+        <v>339.4091631923888</v>
+      </c>
+      <c r="E37">
+        <v>107.6912649478902</v>
+      </c>
+      <c r="F37">
+        <v>107.7508573357515</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>307.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K37">
+        <v>23.3</v>
+      </c>
+      <c r="L37">
+        <v>48.809</v>
+      </c>
+      <c r="M37">
+        <v>5.506068809856902</v>
+      </c>
+      <c r="N37">
+        <v>43.3029311901431</v>
+      </c>
+      <c r="O37">
+        <v>13.85693798084579</v>
+      </c>
+      <c r="P37">
+        <v>29.44599320929731</v>
+      </c>
+      <c r="Q37">
+        <v>52.74599320929731</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.151582267132015</v>
+      </c>
+      <c r="T37">
+        <v>0.8242083587464049</v>
+      </c>
+      <c r="U37">
+        <v>0.0511</v>
+      </c>
+      <c r="V37">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W37">
+        <v>0.03474799999999999</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>8.864582279215742</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.110385578956041</v>
+      </c>
+      <c r="C38">
+        <v>229.5763422949707</v>
+      </c>
+      <c r="D38">
+        <v>340.4057955546008</v>
+      </c>
+      <c r="E38">
+        <v>110.7698608717688</v>
+      </c>
+      <c r="F38">
+        <v>110.8294532596301</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>307.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K38">
+        <v>23.3</v>
+      </c>
+      <c r="L38">
+        <v>48.809</v>
+      </c>
+      <c r="M38">
+        <v>5.663385061567097</v>
+      </c>
+      <c r="N38">
+        <v>43.1456149384329</v>
+      </c>
+      <c r="O38">
+        <v>13.80659678029853</v>
+      </c>
+      <c r="P38">
+        <v>29.33901815813437</v>
+      </c>
+      <c r="Q38">
+        <v>52.63901815813437</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1529317171188141</v>
+      </c>
+      <c r="T38">
+        <v>0.8340700860118107</v>
+      </c>
+      <c r="U38">
+        <v>0.0511</v>
+      </c>
+      <c r="V38">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W38">
+        <v>0.03474799999999999</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>8.618343882570862</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1100808842762724</v>
+      </c>
+      <c r="C39">
+        <v>227.5002489418509</v>
+      </c>
+      <c r="D39">
+        <v>341.4082981253596</v>
+      </c>
+      <c r="E39">
+        <v>113.8484567956474</v>
+      </c>
+      <c r="F39">
+        <v>113.9080491835087</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>307.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K39">
+        <v>23.3</v>
+      </c>
+      <c r="L39">
+        <v>48.809</v>
+      </c>
+      <c r="M39">
+        <v>5.820701313277295</v>
+      </c>
+      <c r="N39">
+        <v>42.9882986867227</v>
+      </c>
+      <c r="O39">
+        <v>13.75625557975127</v>
+      </c>
+      <c r="P39">
+        <v>29.23204310697143</v>
+      </c>
+      <c r="Q39">
+        <v>52.53204310697143</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1543240067877339</v>
+      </c>
+      <c r="T39">
+        <v>0.8442448839840551</v>
+      </c>
+      <c r="U39">
+        <v>0.0511</v>
+      </c>
+      <c r="V39">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W39">
+        <v>0.03474799999999999</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>8.385415669528404</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1097761895965037</v>
+      </c>
+      <c r="C40">
+        <v>225.4300778141492</v>
+      </c>
+      <c r="D40">
+        <v>342.4167229215365</v>
+      </c>
+      <c r="E40">
+        <v>116.927052719526</v>
+      </c>
+      <c r="F40">
+        <v>116.9866451073873</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>307.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K40">
+        <v>23.3</v>
+      </c>
+      <c r="L40">
+        <v>48.809</v>
+      </c>
+      <c r="M40">
+        <v>5.978017564987492</v>
+      </c>
+      <c r="N40">
+        <v>42.83098243501251</v>
+      </c>
+      <c r="O40">
+        <v>13.70591437920401</v>
+      </c>
+      <c r="P40">
+        <v>29.12506805580851</v>
+      </c>
+      <c r="Q40">
+        <v>52.42506805580851</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1557612090266189</v>
+      </c>
+      <c r="T40">
+        <v>0.8547479012457266</v>
+      </c>
+      <c r="U40">
+        <v>0.0511</v>
+      </c>
+      <c r="V40">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W40">
+        <v>0.03474799999999999</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>8.164746836119765</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.109471494916735</v>
+      </c>
+      <c r="C41">
+        <v>223.3658815451313</v>
+      </c>
+      <c r="D41">
+        <v>343.4311225763973</v>
+      </c>
+      <c r="E41">
+        <v>120.0056486434046</v>
+      </c>
+      <c r="F41">
+        <v>120.0652410312659</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>307.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K41">
+        <v>23.3</v>
+      </c>
+      <c r="L41">
+        <v>48.809</v>
+      </c>
+      <c r="M41">
+        <v>6.135333816697689</v>
+      </c>
+      <c r="N41">
+        <v>42.67366618330231</v>
+      </c>
+      <c r="O41">
+        <v>13.65557317865674</v>
+      </c>
+      <c r="P41">
+        <v>29.01809300464557</v>
+      </c>
+      <c r="Q41">
+        <v>52.31809300464557</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1572455326503853</v>
+      </c>
+      <c r="T41">
+        <v>0.8655952797290923</v>
+      </c>
+      <c r="U41">
+        <v>0.0511</v>
+      </c>
+      <c r="V41">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W41">
+        <v>0.03474799999999999</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>7.955394353142334</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1096836002369663</v>
+      </c>
+      <c r="C42">
+        <v>219.5805031566797</v>
+      </c>
+      <c r="D42">
+        <v>342.7243401118242</v>
+      </c>
+      <c r="E42">
+        <v>123.0842445672832</v>
+      </c>
+      <c r="F42">
+        <v>123.1438369551446</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>307.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K42">
+        <v>23.3</v>
+      </c>
+      <c r="L42">
+        <v>48.809</v>
+      </c>
+      <c r="M42">
+        <v>6.526623358622662</v>
+      </c>
+      <c r="N42">
+        <v>42.28237664137733</v>
+      </c>
+      <c r="O42">
+        <v>13.53036052524075</v>
+      </c>
+      <c r="P42">
+        <v>28.75201611613658</v>
+      </c>
+      <c r="Q42">
+        <v>52.05201611613658</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1587793337282772</v>
+      </c>
+      <c r="T42">
+        <v>0.8768042374952369</v>
+      </c>
+      <c r="U42">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V42">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W42">
+        <v>0.03604</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>7.478445946404412</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1093918255571976</v>
+      </c>
+      <c r="C43">
+        <v>217.4749195597522</v>
+      </c>
+      <c r="D43">
+        <v>343.6973524387753</v>
+      </c>
+      <c r="E43">
+        <v>126.1628404911618</v>
+      </c>
+      <c r="F43">
+        <v>126.2224328790232</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>307.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K43">
+        <v>23.3</v>
+      </c>
+      <c r="L43">
+        <v>48.809</v>
+      </c>
+      <c r="M43">
+        <v>6.689788942588229</v>
+      </c>
+      <c r="N43">
+        <v>42.11921105741177</v>
+      </c>
+      <c r="O43">
+        <v>13.47814753837177</v>
+      </c>
+      <c r="P43">
+        <v>28.64106351904</v>
+      </c>
+      <c r="Q43">
+        <v>51.94106351904</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1603651280630469</v>
+      </c>
+      <c r="T43">
+        <v>0.8883931599314202</v>
+      </c>
+      <c r="U43">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V43">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W43">
+        <v>0.03604</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>7.296044825760402</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.109100050877429</v>
+      </c>
+      <c r="C44">
+        <v>215.3748765586403</v>
+      </c>
+      <c r="D44">
+        <v>344.6759053615421</v>
+      </c>
+      <c r="E44">
+        <v>129.2414364150405</v>
+      </c>
+      <c r="F44">
+        <v>129.3010288029018</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>307.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K44">
+        <v>23.3</v>
+      </c>
+      <c r="L44">
+        <v>48.809</v>
+      </c>
+      <c r="M44">
+        <v>6.852954526553795</v>
+      </c>
+      <c r="N44">
+        <v>41.9560454734462</v>
+      </c>
+      <c r="O44">
+        <v>13.42593455150279</v>
+      </c>
+      <c r="P44">
+        <v>28.53011092194341</v>
+      </c>
+      <c r="Q44">
+        <v>51.83011092194342</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1620056049610845</v>
+      </c>
+      <c r="T44">
+        <v>0.9003817003826444</v>
+      </c>
+      <c r="U44">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V44">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W44">
+        <v>0.03604</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>7.122329472766107</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1088082761976603</v>
+      </c>
+      <c r="C45">
+        <v>213.2804216129491</v>
+      </c>
+      <c r="D45">
+        <v>345.6600463397295</v>
+      </c>
+      <c r="E45">
+        <v>132.320032338919</v>
+      </c>
+      <c r="F45">
+        <v>132.3796247267804</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>307.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K45">
+        <v>23.3</v>
+      </c>
+      <c r="L45">
+        <v>48.809</v>
+      </c>
+      <c r="M45">
+        <v>7.016120110519361</v>
+      </c>
+      <c r="N45">
+        <v>41.79287988948064</v>
+      </c>
+      <c r="O45">
+        <v>13.37372156463381</v>
+      </c>
+      <c r="P45">
+        <v>28.41915832484683</v>
+      </c>
+      <c r="Q45">
+        <v>51.71915832484683</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1637036424520356</v>
+      </c>
+      <c r="T45">
+        <v>0.9127908913760168</v>
+      </c>
+      <c r="U45">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V45">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W45">
+        <v>0.03604</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>6.956693903632012</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1085165015178916</v>
+      </c>
+      <c r="C46">
+        <v>211.1916027258739</v>
+      </c>
+      <c r="D46">
+        <v>346.6498233765329</v>
+      </c>
+      <c r="E46">
+        <v>135.3986282627977</v>
+      </c>
+      <c r="F46">
+        <v>135.458220650659</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>307.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K46">
+        <v>23.3</v>
+      </c>
+      <c r="L46">
+        <v>48.809</v>
+      </c>
+      <c r="M46">
+        <v>7.179285694484927</v>
+      </c>
+      <c r="N46">
+        <v>41.62971430551507</v>
+      </c>
+      <c r="O46">
+        <v>13.32150857776483</v>
+      </c>
+      <c r="P46">
+        <v>28.30820572775025</v>
+      </c>
+      <c r="Q46">
+        <v>51.60820572775025</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1654623241390921</v>
+      </c>
+      <c r="T46">
+        <v>0.9256432677620096</v>
+      </c>
+      <c r="U46">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V46">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W46">
+        <v>0.03604</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>6.798587224004012</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1082247268381229</v>
+      </c>
+      <c r="C47">
+        <v>209.1084684520062</v>
+      </c>
+      <c r="D47">
+        <v>347.6452850265438</v>
+      </c>
+      <c r="E47">
+        <v>138.4772241866763</v>
+      </c>
+      <c r="F47">
+        <v>138.5368165745376</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>307.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K47">
+        <v>23.3</v>
+      </c>
+      <c r="L47">
+        <v>48.809</v>
+      </c>
+      <c r="M47">
+        <v>7.342451278450495</v>
+      </c>
+      <c r="N47">
+        <v>41.4665487215495</v>
+      </c>
+      <c r="O47">
+        <v>13.26929559089584</v>
+      </c>
+      <c r="P47">
+        <v>28.19725313065366</v>
+      </c>
+      <c r="Q47">
+        <v>51.49725313065366</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1672849578874962</v>
+      </c>
+      <c r="T47">
+        <v>0.9389630032893111</v>
+      </c>
+      <c r="U47">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V47">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W47">
+        <v>0.03604</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>6.647507507915033</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1079329521583543</v>
+      </c>
+      <c r="C48">
+        <v>207.0310679052739</v>
+      </c>
+      <c r="D48">
+        <v>348.6464804036901</v>
+      </c>
+      <c r="E48">
+        <v>141.5558201105549</v>
+      </c>
+      <c r="F48">
+        <v>141.6154124984162</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>307.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K48">
+        <v>23.3</v>
+      </c>
+      <c r="L48">
+        <v>48.809</v>
+      </c>
+      <c r="M48">
+        <v>7.505616862416062</v>
+      </c>
+      <c r="N48">
+        <v>41.30338313758394</v>
+      </c>
+      <c r="O48">
+        <v>13.21708260402686</v>
+      </c>
+      <c r="P48">
+        <v>28.08630053355707</v>
+      </c>
+      <c r="Q48">
+        <v>51.38630053355708</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1691750965895449</v>
+      </c>
+      <c r="T48">
+        <v>0.9527760623546612</v>
+      </c>
+      <c r="U48">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V48">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W48">
+        <v>0.03604</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>6.502996475134271</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1076411774785856</v>
+      </c>
+      <c r="C49">
+        <v>204.9594507670183</v>
+      </c>
+      <c r="D49">
+        <v>349.6534591893131</v>
+      </c>
+      <c r="E49">
+        <v>144.6344160344335</v>
+      </c>
+      <c r="F49">
+        <v>144.6940084222948</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>307.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K49">
+        <v>23.3</v>
+      </c>
+      <c r="L49">
+        <v>48.809</v>
+      </c>
+      <c r="M49">
+        <v>7.668782446381628</v>
+      </c>
+      <c r="N49">
+        <v>41.14021755361837</v>
+      </c>
+      <c r="O49">
+        <v>13.16486961715788</v>
+      </c>
+      <c r="P49">
+        <v>27.97534793646049</v>
+      </c>
+      <c r="Q49">
+        <v>51.27534793646049</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1711365612803501</v>
+      </c>
+      <c r="T49">
+        <v>0.9671103689319109</v>
+      </c>
+      <c r="U49">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V49">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W49">
+        <v>0.03604</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>6.364634848003755</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1073494027988169</v>
+      </c>
+      <c r="C50">
+        <v>202.8936672942119</v>
+      </c>
+      <c r="D50">
+        <v>350.6662716403853</v>
+      </c>
+      <c r="E50">
+        <v>147.7130119583121</v>
+      </c>
+      <c r="F50">
+        <v>147.7726043461734</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>307.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K50">
+        <v>23.3</v>
+      </c>
+      <c r="L50">
+        <v>48.809</v>
+      </c>
+      <c r="M50">
+        <v>7.831948030347193</v>
+      </c>
+      <c r="N50">
+        <v>40.97705196965281</v>
+      </c>
+      <c r="O50">
+        <v>13.1126566302889</v>
+      </c>
+      <c r="P50">
+        <v>27.86439533936391</v>
+      </c>
+      <c r="Q50">
+        <v>51.16439533936391</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1731734669208017</v>
+      </c>
+      <c r="T50">
+        <v>0.9819959949929011</v>
+      </c>
+      <c r="U50">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V50">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W50">
+        <v>0.03604</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>6.232038288670345</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1077240281190482</v>
+      </c>
+      <c r="C51">
+        <v>198.5157322169112</v>
+      </c>
+      <c r="D51">
+        <v>349.3669324869633</v>
+      </c>
+      <c r="E51">
+        <v>150.7916078821907</v>
+      </c>
+      <c r="F51">
+        <v>150.8512002700521</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>307.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K51">
+        <v>23.3</v>
+      </c>
+      <c r="L51">
+        <v>48.809</v>
+      </c>
+      <c r="M51">
+        <v>8.296816014852864</v>
+      </c>
+      <c r="N51">
+        <v>40.51218398514713</v>
+      </c>
+      <c r="O51">
+        <v>12.96389887524708</v>
+      </c>
+      <c r="P51">
+        <v>27.54828510990005</v>
+      </c>
+      <c r="Q51">
+        <v>50.84828510990005</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.17529025121382</v>
+      </c>
+      <c r="T51">
+        <v>0.9974653710954988</v>
+      </c>
+      <c r="U51">
+        <v>0.055</v>
+      </c>
+      <c r="V51">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W51">
+        <v>0.0374</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>5.882859148934084</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1074458534392795</v>
+      </c>
+      <c r="C52">
+        <v>196.4010260107142</v>
+      </c>
+      <c r="D52">
+        <v>350.3308222046448</v>
+      </c>
+      <c r="E52">
+        <v>153.8702038060694</v>
+      </c>
+      <c r="F52">
+        <v>153.9297961939307</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>307.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K52">
+        <v>23.3</v>
+      </c>
+      <c r="L52">
+        <v>48.809</v>
+      </c>
+      <c r="M52">
+        <v>8.466138790666188</v>
+      </c>
+      <c r="N52">
+        <v>40.34286120933381</v>
+      </c>
+      <c r="O52">
+        <v>12.90971558698682</v>
+      </c>
+      <c r="P52">
+        <v>27.43314562234699</v>
+      </c>
+      <c r="Q52">
+        <v>50.733145622347</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.177491706878559</v>
+      </c>
+      <c r="T52">
+        <v>1.013553522242201</v>
+      </c>
+      <c r="U52">
+        <v>0.055</v>
+      </c>
+      <c r="V52">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W52">
+        <v>0.0374</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>5.765201965955403</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1071676787595108</v>
+      </c>
+      <c r="C53">
+        <v>194.2916531872596</v>
+      </c>
+      <c r="D53">
+        <v>351.3000453050689</v>
+      </c>
+      <c r="E53">
+        <v>156.948799729948</v>
+      </c>
+      <c r="F53">
+        <v>157.0083921178093</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>307.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K53">
+        <v>23.3</v>
+      </c>
+      <c r="L53">
+        <v>48.809</v>
+      </c>
+      <c r="M53">
+        <v>8.635461566479512</v>
+      </c>
+      <c r="N53">
+        <v>40.17353843352048</v>
+      </c>
+      <c r="O53">
+        <v>12.85553229872656</v>
+      </c>
+      <c r="P53">
+        <v>27.31800613479393</v>
+      </c>
+      <c r="Q53">
+        <v>50.61800613479393</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1797830178765527</v>
+      </c>
+      <c r="T53">
+        <v>1.03029833261938</v>
+      </c>
+      <c r="U53">
+        <v>0.055</v>
+      </c>
+      <c r="V53">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W53">
+        <v>0.0374</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>5.652158790152355</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1068895040797421</v>
+      </c>
+      <c r="C54">
+        <v>192.1876581352647</v>
+      </c>
+      <c r="D54">
+        <v>352.2746461769527</v>
+      </c>
+      <c r="E54">
+        <v>160.0273956538266</v>
+      </c>
+      <c r="F54">
+        <v>160.0869880416879</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>307.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K54">
+        <v>23.3</v>
+      </c>
+      <c r="L54">
+        <v>48.809</v>
+      </c>
+      <c r="M54">
+        <v>8.804784342292836</v>
+      </c>
+      <c r="N54">
+        <v>40.00421565770716</v>
+      </c>
+      <c r="O54">
+        <v>12.80134901046629</v>
+      </c>
+      <c r="P54">
+        <v>27.20286664724087</v>
+      </c>
+      <c r="Q54">
+        <v>50.50286664724086</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1821698001661295</v>
+      </c>
+      <c r="T54">
+        <v>1.047740843428941</v>
+      </c>
+      <c r="U54">
+        <v>0.055</v>
+      </c>
+      <c r="V54">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W54">
+        <v>0.0374</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>5.543463428803271</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1066113293999735</v>
+      </c>
+      <c r="C55">
+        <v>190.0890857374021</v>
+      </c>
+      <c r="D55">
+        <v>353.2546697029687</v>
+      </c>
+      <c r="E55">
+        <v>163.1059915777052</v>
+      </c>
+      <c r="F55">
+        <v>163.1655839655665</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>307.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K55">
+        <v>23.3</v>
+      </c>
+      <c r="L55">
+        <v>48.809</v>
+      </c>
+      <c r="M55">
+        <v>8.97410711810616</v>
+      </c>
+      <c r="N55">
+        <v>39.83489288189384</v>
+      </c>
+      <c r="O55">
+        <v>12.74716572220603</v>
+      </c>
+      <c r="P55">
+        <v>27.08772715968781</v>
+      </c>
+      <c r="Q55">
+        <v>50.38772715968781</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.184658147659518</v>
+      </c>
+      <c r="T55">
+        <v>1.065925588741038</v>
+      </c>
+      <c r="U55">
+        <v>0.055</v>
+      </c>
+      <c r="V55">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W55">
+        <v>0.0374</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>5.438869779203209</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1063331547202048</v>
+      </c>
+      <c r="C56">
+        <v>187.9959813771903</v>
+      </c>
+      <c r="D56">
+        <v>354.2401612666354</v>
+      </c>
+      <c r="E56">
+        <v>166.1845875015838</v>
+      </c>
+      <c r="F56">
+        <v>166.2441798894451</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>307.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K56">
+        <v>23.3</v>
+      </c>
+      <c r="L56">
+        <v>48.809</v>
+      </c>
+      <c r="M56">
+        <v>9.143429893919484</v>
+      </c>
+      <c r="N56">
+        <v>39.66557010608052</v>
+      </c>
+      <c r="O56">
+        <v>12.69298243394577</v>
+      </c>
+      <c r="P56">
+        <v>26.97258767213475</v>
+      </c>
+      <c r="Q56">
+        <v>50.27258767213475</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1872546841743582</v>
+      </c>
+      <c r="T56">
+        <v>1.08490097515366</v>
+      </c>
+      <c r="U56">
+        <v>0.055</v>
+      </c>
+      <c r="V56">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W56">
+        <v>0.0374</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>5.338149968477224</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1060549800404361</v>
+      </c>
+      <c r="C57">
+        <v>185.9083909459981</v>
+      </c>
+      <c r="D57">
+        <v>355.2311667593219</v>
+      </c>
+      <c r="E57">
+        <v>169.2631834254624</v>
+      </c>
+      <c r="F57">
+        <v>169.3227758133238</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>307.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K57">
+        <v>23.3</v>
+      </c>
+      <c r="L57">
+        <v>48.809</v>
+      </c>
+      <c r="M57">
+        <v>9.312752669732808</v>
+      </c>
+      <c r="N57">
+        <v>39.49624733026719</v>
+      </c>
+      <c r="O57">
+        <v>12.6387991456855</v>
+      </c>
+      <c r="P57">
+        <v>26.85744818458168</v>
+      </c>
+      <c r="Q57">
+        <v>50.15744818458168</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1899666223120802</v>
+      </c>
+      <c r="T57">
+        <v>1.10471971207351</v>
+      </c>
+      <c r="U57">
+        <v>0.055</v>
+      </c>
+      <c r="V57">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W57">
+        <v>0.0374</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>5.241092696323093</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1057768053606674</v>
+      </c>
+      <c r="C58">
+        <v>183.8263608501698</v>
+      </c>
+      <c r="D58">
+        <v>356.2277325873722</v>
+      </c>
+      <c r="E58">
+        <v>172.3417793493411</v>
+      </c>
+      <c r="F58">
+        <v>172.4013717372024</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>307.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K58">
+        <v>23.3</v>
+      </c>
+      <c r="L58">
+        <v>48.809</v>
+      </c>
+      <c r="M58">
+        <v>9.482075445546132</v>
+      </c>
+      <c r="N58">
+        <v>39.32692455445387</v>
+      </c>
+      <c r="O58">
+        <v>12.58461585742524</v>
+      </c>
+      <c r="P58">
+        <v>26.74230869702863</v>
+      </c>
+      <c r="Q58">
+        <v>50.04230869702863</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1928018303651532</v>
+      </c>
+      <c r="T58">
+        <v>1.125439300671534</v>
+      </c>
+      <c r="U58">
+        <v>0.055</v>
+      </c>
+      <c r="V58">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W58">
+        <v>0.0374</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>5.147501755317323</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1054986306808987</v>
+      </c>
+      <c r="C59">
+        <v>181.7499380182678</v>
+      </c>
+      <c r="D59">
+        <v>357.2299056793487</v>
+      </c>
+      <c r="E59">
+        <v>175.4203752732197</v>
+      </c>
+      <c r="F59">
+        <v>175.479967661081</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>307.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K59">
+        <v>23.3</v>
+      </c>
+      <c r="L59">
+        <v>48.809</v>
+      </c>
+      <c r="M59">
+        <v>9.651398221359454</v>
+      </c>
+      <c r="N59">
+        <v>39.15760177864054</v>
+      </c>
+      <c r="O59">
+        <v>12.53043256916498</v>
+      </c>
+      <c r="P59">
+        <v>26.62716920947556</v>
+      </c>
+      <c r="Q59">
+        <v>49.92716920947557</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1957689085602296</v>
+      </c>
+      <c r="T59">
+        <v>1.147122591064816</v>
+      </c>
+      <c r="U59">
+        <v>0.055</v>
+      </c>
+      <c r="V59">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W59">
+        <v>0.0374</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>5.057194706978422</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.10522045600113</v>
+      </c>
+      <c r="C60">
+        <v>179.67916990844</v>
+      </c>
+      <c r="D60">
+        <v>358.2377334933996</v>
+      </c>
+      <c r="E60">
+        <v>178.4989711970983</v>
+      </c>
+      <c r="F60">
+        <v>178.5585635849596</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>307.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K60">
+        <v>23.3</v>
+      </c>
+      <c r="L60">
+        <v>48.809</v>
+      </c>
+      <c r="M60">
+        <v>9.820720997172778</v>
+      </c>
+      <c r="N60">
+        <v>38.98827900282722</v>
+      </c>
+      <c r="O60">
+        <v>12.47624928090471</v>
+      </c>
+      <c r="P60">
+        <v>26.51202972192251</v>
+      </c>
+      <c r="Q60">
+        <v>49.81202972192251</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1988772761931668</v>
+      </c>
+      <c r="T60">
+        <v>1.169838419095873</v>
+      </c>
+      <c r="U60">
+        <v>0.055</v>
+      </c>
+      <c r="V60">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W60">
+        <v>0.0374</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>4.97000169478914</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1049422813213614</v>
+      </c>
+      <c r="C61">
+        <v>177.6141045159105</v>
+      </c>
+      <c r="D61">
+        <v>359.2512640247487</v>
+      </c>
+      <c r="E61">
+        <v>181.5775671209769</v>
+      </c>
+      <c r="F61">
+        <v>181.6371595088382</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>307.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K61">
+        <v>23.3</v>
+      </c>
+      <c r="L61">
+        <v>48.809</v>
+      </c>
+      <c r="M61">
+        <v>9.990043772986102</v>
+      </c>
+      <c r="N61">
+        <v>38.8189562270139</v>
+      </c>
+      <c r="O61">
+        <v>12.42206599264445</v>
+      </c>
+      <c r="P61">
+        <v>26.39689023436945</v>
+      </c>
+      <c r="Q61">
+        <v>49.69689023436945</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2021372715155155</v>
+      </c>
+      <c r="T61">
+        <v>1.193662336299177</v>
+      </c>
+      <c r="U61">
+        <v>0.055</v>
+      </c>
+      <c r="V61">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W61">
+        <v>0.0374</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>4.885764377928307</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1046641066415927</v>
+      </c>
+      <c r="C62">
+        <v>175.5547903805998</v>
+      </c>
+      <c r="D62">
+        <v>360.2705458133166</v>
+      </c>
+      <c r="E62">
+        <v>184.6561630448555</v>
+      </c>
+      <c r="F62">
+        <v>184.7157554327168</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>307.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K62">
+        <v>23.3</v>
+      </c>
+      <c r="L62">
+        <v>48.809</v>
+      </c>
+      <c r="M62">
+        <v>10.15936654879942</v>
+      </c>
+      <c r="N62">
+        <v>38.64963345120057</v>
+      </c>
+      <c r="O62">
+        <v>12.36788270438418</v>
+      </c>
+      <c r="P62">
+        <v>26.28175074681639</v>
+      </c>
+      <c r="Q62">
+        <v>49.58175074681638</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2055602666039816</v>
+      </c>
+      <c r="T62">
+        <v>1.218677449362646</v>
+      </c>
+      <c r="U62">
+        <v>0.055</v>
+      </c>
+      <c r="V62">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W62">
+        <v>0.0374</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>4.804334971629503</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.104385931961824</v>
+      </c>
+      <c r="C63">
+        <v>173.5012765948727</v>
+      </c>
+      <c r="D63">
+        <v>361.2956279514681</v>
+      </c>
+      <c r="E63">
+        <v>187.7347589687341</v>
+      </c>
+      <c r="F63">
+        <v>187.7943513565954</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>307.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K63">
+        <v>23.3</v>
+      </c>
+      <c r="L63">
+        <v>48.809</v>
+      </c>
+      <c r="M63">
+        <v>10.32868932461275</v>
+      </c>
+      <c r="N63">
+        <v>38.48031067538725</v>
+      </c>
+      <c r="O63">
+        <v>12.31369941612392</v>
+      </c>
+      <c r="P63">
+        <v>26.16661125926333</v>
+      </c>
+      <c r="Q63">
+        <v>49.46661125926333</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2091587999021128</v>
+      </c>
+      <c r="T63">
+        <v>1.244975388737062</v>
+      </c>
+      <c r="U63">
+        <v>0.055</v>
+      </c>
+      <c r="V63">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W63">
+        <v>0.0374</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>4.725575381930659</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1041077572820553</v>
+      </c>
+      <c r="C64">
+        <v>171.4536128114209</v>
+      </c>
+      <c r="D64">
+        <v>362.326560091895</v>
+      </c>
+      <c r="E64">
+        <v>190.8133548926127</v>
+      </c>
+      <c r="F64">
+        <v>190.8729472804741</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>307.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K64">
+        <v>23.3</v>
+      </c>
+      <c r="L64">
+        <v>48.809</v>
+      </c>
+      <c r="M64">
+        <v>10.49801210042607</v>
+      </c>
+      <c r="N64">
+        <v>38.31098789957392</v>
+      </c>
+      <c r="O64">
+        <v>12.25951612786366</v>
+      </c>
+      <c r="P64">
+        <v>26.05147177171026</v>
+      </c>
+      <c r="Q64">
+        <v>49.35147177171027</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2129467296896192</v>
+      </c>
+      <c r="T64">
+        <v>1.272657430183815</v>
+      </c>
+      <c r="U64">
+        <v>0.055</v>
+      </c>
+      <c r="V64">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W64">
+        <v>0.0374</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>4.649356424157583</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1038295826022866</v>
+      </c>
+      <c r="C65">
+        <v>169.41184925128</v>
+      </c>
+      <c r="D65">
+        <v>363.3633924556327</v>
+      </c>
+      <c r="E65">
+        <v>193.8919508164913</v>
+      </c>
+      <c r="F65">
+        <v>193.9515432043527</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>307.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K65">
+        <v>23.3</v>
+      </c>
+      <c r="L65">
+        <v>48.809</v>
+      </c>
+      <c r="M65">
+        <v>10.6673348762394</v>
+      </c>
+      <c r="N65">
+        <v>38.1416651237606</v>
+      </c>
+      <c r="O65">
+        <v>12.2053328396034</v>
+      </c>
+      <c r="P65">
+        <v>25.93633228415721</v>
+      </c>
+      <c r="Q65">
+        <v>49.23633228415721</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2169394124386125</v>
+      </c>
+      <c r="T65">
+        <v>1.301835798195259</v>
+      </c>
+      <c r="U65">
+        <v>0.055</v>
+      </c>
+      <c r="V65">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W65">
+        <v>0.0374</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>4.57555711583762</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1035514079225179</v>
+      </c>
+      <c r="C66">
+        <v>167.3760367119849</v>
+      </c>
+      <c r="D66">
+        <v>364.4061758402161</v>
+      </c>
+      <c r="E66">
+        <v>196.9705467403699</v>
+      </c>
+      <c r="F66">
+        <v>197.0301391282313</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>307.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K66">
+        <v>23.3</v>
+      </c>
+      <c r="L66">
+        <v>48.809</v>
+      </c>
+      <c r="M66">
+        <v>10.83665765205272</v>
+      </c>
+      <c r="N66">
+        <v>37.97234234794728</v>
+      </c>
+      <c r="O66">
+        <v>12.15114955134313</v>
+      </c>
+      <c r="P66">
+        <v>25.82119279660414</v>
+      </c>
+      <c r="Q66">
+        <v>49.12119279660415</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2211539108958831</v>
+      </c>
+      <c r="T66">
+        <v>1.332635186651782</v>
+      </c>
+      <c r="U66">
+        <v>0.055</v>
+      </c>
+      <c r="V66">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W66">
+        <v>0.0374</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>4.504064035902658</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1049528332427492</v>
+      </c>
+      <c r="C67">
+        <v>159.1039783713264</v>
+      </c>
+      <c r="D67">
+        <v>359.2127134234363</v>
+      </c>
+      <c r="E67">
+        <v>200.0491426642486</v>
+      </c>
+      <c r="F67">
+        <v>200.1087350521099</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>307.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K67">
+        <v>23.3</v>
+      </c>
+      <c r="L67">
+        <v>48.809</v>
+      </c>
+      <c r="M67">
+        <v>11.76639362106406</v>
+      </c>
+      <c r="N67">
+        <v>37.04260637893594</v>
+      </c>
+      <c r="O67">
+        <v>11.8536340412595</v>
+      </c>
+      <c r="P67">
+        <v>25.18897233767643</v>
+      </c>
+      <c r="Q67">
+        <v>48.48897233767643</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2256092378364264</v>
+      </c>
+      <c r="T67">
+        <v>1.365194540162964</v>
+      </c>
+      <c r="U67">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V67">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W67">
+        <v>0.039984</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>4.14816991270993</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1047004985629806</v>
+      </c>
+      <c r="C68">
+        <v>156.9495396087925</v>
+      </c>
+      <c r="D68">
+        <v>360.136870584781</v>
+      </c>
+      <c r="E68">
+        <v>203.1277385881272</v>
+      </c>
+      <c r="F68">
+        <v>203.1873309759885</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>307.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K68">
+        <v>23.3</v>
+      </c>
+      <c r="L68">
+        <v>48.809</v>
+      </c>
+      <c r="M68">
+        <v>11.94741506138813</v>
+      </c>
+      <c r="N68">
+        <v>36.86158493861187</v>
+      </c>
+      <c r="O68">
+        <v>11.7957071803558</v>
+      </c>
+      <c r="P68">
+        <v>25.06587775825607</v>
+      </c>
+      <c r="Q68">
+        <v>48.36587775825608</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2303266428322958</v>
+      </c>
+      <c r="T68">
+        <v>1.399669149763039</v>
+      </c>
+      <c r="U68">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V68">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W68">
+        <v>0.039984</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>4.085318853426447</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1044481638832119</v>
+      </c>
+      <c r="C69">
+        <v>154.7998683245604</v>
+      </c>
+      <c r="D69">
+        <v>361.0657952244275</v>
+      </c>
+      <c r="E69">
+        <v>206.2063345120058</v>
+      </c>
+      <c r="F69">
+        <v>206.2659268998671</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>307.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K69">
+        <v>23.3</v>
+      </c>
+      <c r="L69">
+        <v>48.809</v>
+      </c>
+      <c r="M69">
+        <v>12.12843650171219</v>
+      </c>
+      <c r="N69">
+        <v>36.68056349828781</v>
+      </c>
+      <c r="O69">
+        <v>11.7377803194521</v>
+      </c>
+      <c r="P69">
+        <v>24.94278317883571</v>
+      </c>
+      <c r="Q69">
+        <v>48.24278317883571</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2353299511612482</v>
+      </c>
+      <c r="T69">
+        <v>1.436233129641906</v>
+      </c>
+      <c r="U69">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V69">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W69">
+        <v>0.039984</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>4.024343945166351</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1061379092034432</v>
+      </c>
+      <c r="C70">
+        <v>145.5906267262135</v>
+      </c>
+      <c r="D70">
+        <v>354.9351495499592</v>
+      </c>
+      <c r="E70">
+        <v>209.2849304358844</v>
+      </c>
+      <c r="F70">
+        <v>209.3445228237457</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>307.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K70">
+        <v>23.3</v>
+      </c>
+      <c r="L70">
+        <v>48.809</v>
+      </c>
+      <c r="M70">
+        <v>13.18870493789598</v>
+      </c>
+      <c r="N70">
+        <v>35.62029506210402</v>
+      </c>
+      <c r="O70">
+        <v>11.39849441987329</v>
+      </c>
+      <c r="P70">
+        <v>24.22180064223073</v>
+      </c>
+      <c r="Q70">
+        <v>47.52180064223073</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.24064596626076</v>
+      </c>
+      <c r="T70">
+        <v>1.475082358263203</v>
+      </c>
+      <c r="U70">
+        <v>0.063</v>
+      </c>
+      <c r="V70">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W70">
+        <v>0.04284</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>3.7008182554569</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1059141345236745</v>
+      </c>
+      <c r="C71">
+        <v>143.3119317627666</v>
+      </c>
+      <c r="D71">
+        <v>355.735050510391</v>
+      </c>
+      <c r="E71">
+        <v>212.363526359763</v>
+      </c>
+      <c r="F71">
+        <v>212.4231187476244</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>307.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K71">
+        <v>23.3</v>
+      </c>
+      <c r="L71">
+        <v>48.809</v>
+      </c>
+      <c r="M71">
+        <v>13.38265648110034</v>
+      </c>
+      <c r="N71">
+        <v>35.42634351889966</v>
+      </c>
+      <c r="O71">
+        <v>11.3364299260479</v>
+      </c>
+      <c r="P71">
+        <v>24.08991359285177</v>
+      </c>
+      <c r="Q71">
+        <v>47.38991359285177</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2463049500763694</v>
+      </c>
+      <c r="T71">
+        <v>1.516437988731034</v>
+      </c>
+      <c r="U71">
+        <v>0.063</v>
+      </c>
+      <c r="V71">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W71">
+        <v>0.04284</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>3.647183208276364</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1056903598439058</v>
+      </c>
+      <c r="C72">
+        <v>141.0368503427276</v>
+      </c>
+      <c r="D72">
+        <v>356.5385650142306</v>
+      </c>
+      <c r="E72">
+        <v>215.4421222836417</v>
+      </c>
+      <c r="F72">
+        <v>215.501714671503</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>307.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K72">
+        <v>23.3</v>
+      </c>
+      <c r="L72">
+        <v>48.809</v>
+      </c>
+      <c r="M72">
+        <v>13.57660802430469</v>
+      </c>
+      <c r="N72">
+        <v>35.23239197569531</v>
+      </c>
+      <c r="O72">
+        <v>11.2743654322225</v>
+      </c>
+      <c r="P72">
+        <v>23.9580265434728</v>
+      </c>
+      <c r="Q72">
+        <v>47.25802654347281</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2523411994796861</v>
+      </c>
+      <c r="T72">
+        <v>1.560550661230055</v>
+      </c>
+      <c r="U72">
+        <v>0.063</v>
+      </c>
+      <c r="V72">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W72">
+        <v>0.04284</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>3.595080591015273</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1054665851641371</v>
+      </c>
+      <c r="C73">
+        <v>138.765407007741</v>
+      </c>
+      <c r="D73">
+        <v>357.3457176031226</v>
+      </c>
+      <c r="E73">
+        <v>218.5207182075202</v>
+      </c>
+      <c r="F73">
+        <v>218.5803105953815</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>307.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K73">
+        <v>23.3</v>
+      </c>
+      <c r="L73">
+        <v>48.809</v>
+      </c>
+      <c r="M73">
+        <v>13.77055956750904</v>
+      </c>
+      <c r="N73">
+        <v>35.03844043249096</v>
+      </c>
+      <c r="O73">
+        <v>11.21230093839711</v>
+      </c>
+      <c r="P73">
+        <v>23.82613949409385</v>
+      </c>
+      <c r="Q73">
+        <v>47.12613949409385</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2587937419453005</v>
+      </c>
+      <c r="T73">
+        <v>1.60770558700487</v>
+      </c>
+      <c r="U73">
+        <v>0.063</v>
+      </c>
+      <c r="V73">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W73">
+        <v>0.04284</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>3.54444565311365</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1087189704843685</v>
+      </c>
+      <c r="C74">
+        <v>124.3034876999278</v>
+      </c>
+      <c r="D74">
+        <v>345.962394219188</v>
+      </c>
+      <c r="E74">
+        <v>221.5993141313988</v>
+      </c>
+      <c r="F74">
+        <v>221.6589065192602</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>307.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K74">
+        <v>23.3</v>
+      </c>
+      <c r="L74">
+        <v>48.809</v>
+      </c>
+      <c r="M74">
+        <v>15.53828934700014</v>
+      </c>
+      <c r="N74">
+        <v>33.27071065299986</v>
+      </c>
+      <c r="O74">
+        <v>10.64662740895996</v>
+      </c>
+      <c r="P74">
+        <v>22.6240832440399</v>
+      </c>
+      <c r="Q74">
+        <v>45.92408324403991</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2657071803013159</v>
+      </c>
+      <c r="T74">
+        <v>1.6582287217636</v>
+      </c>
+      <c r="U74">
+        <v>0.0701</v>
+      </c>
+      <c r="V74">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W74">
+        <v>0.047668</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>3.141208077028324</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1085434758045998</v>
+      </c>
+      <c r="C75">
+        <v>121.8205792744334</v>
+      </c>
+      <c r="D75">
+        <v>346.5580817175722</v>
+      </c>
+      <c r="E75">
+        <v>224.6779100552775</v>
+      </c>
+      <c r="F75">
+        <v>224.7375024431388</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>307.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K75">
+        <v>23.3</v>
+      </c>
+      <c r="L75">
+        <v>48.809</v>
+      </c>
+      <c r="M75">
+        <v>15.75409892126403</v>
+      </c>
+      <c r="N75">
+        <v>33.05490107873597</v>
+      </c>
+      <c r="O75">
+        <v>10.57756834519551</v>
+      </c>
+      <c r="P75">
+        <v>22.47733273354046</v>
+      </c>
+      <c r="Q75">
+        <v>45.77733273354046</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2731327252022214</v>
+      </c>
+      <c r="T75">
+        <v>1.712494310948903</v>
+      </c>
+      <c r="U75">
+        <v>0.0701</v>
+      </c>
+      <c r="V75">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W75">
+        <v>0.047668</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>3.098177829397799</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1083679811248311</v>
+      </c>
+      <c r="C76">
+        <v>119.3397257290929</v>
+      </c>
+      <c r="D76">
+        <v>347.1558240961103</v>
+      </c>
+      <c r="E76">
+        <v>227.7565059791561</v>
+      </c>
+      <c r="F76">
+        <v>227.8160983670174</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>307.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K76">
+        <v>23.3</v>
+      </c>
+      <c r="L76">
+        <v>48.809</v>
+      </c>
+      <c r="M76">
+        <v>15.96990849552792</v>
+      </c>
+      <c r="N76">
+        <v>32.83909150447208</v>
+      </c>
+      <c r="O76">
+        <v>10.50850928143107</v>
+      </c>
+      <c r="P76">
+        <v>22.33058222304101</v>
+      </c>
+      <c r="Q76">
+        <v>45.63058222304102</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.281129465864735</v>
+      </c>
+      <c r="T76">
+        <v>1.770934176225383</v>
+      </c>
+      <c r="U76">
+        <v>0.0701</v>
+      </c>
+      <c r="V76">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W76">
+        <v>0.047668</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>3.056310561432964</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1081924864450624</v>
+      </c>
+      <c r="C77">
+        <v>116.8609377150314</v>
+      </c>
+      <c r="D77">
+        <v>347.7556320059275</v>
+      </c>
+      <c r="E77">
+        <v>230.8351019030347</v>
+      </c>
+      <c r="F77">
+        <v>230.894694290896</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>307.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K77">
+        <v>23.3</v>
+      </c>
+      <c r="L77">
+        <v>48.809</v>
+      </c>
+      <c r="M77">
+        <v>16.18571806979181</v>
+      </c>
+      <c r="N77">
+        <v>32.62328193020819</v>
+      </c>
+      <c r="O77">
+        <v>10.43945021766662</v>
+      </c>
+      <c r="P77">
+        <v>22.18383171254156</v>
+      </c>
+      <c r="Q77">
+        <v>45.48383171254157</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2897659457802496</v>
+      </c>
+      <c r="T77">
+        <v>1.834049230723982</v>
+      </c>
+      <c r="U77">
+        <v>0.0701</v>
+      </c>
+      <c r="V77">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W77">
+        <v>0.047668</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>3.015559753947191</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1190248317652937</v>
+      </c>
+      <c r="C78">
+        <v>80.26947628163265</v>
+      </c>
+      <c r="D78">
+        <v>314.2427664964073</v>
+      </c>
+      <c r="E78">
+        <v>233.9136978269133</v>
+      </c>
+      <c r="F78">
+        <v>233.9732902147746</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>307.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K78">
+        <v>23.3</v>
+      </c>
+      <c r="L78">
+        <v>48.809</v>
+      </c>
+      <c r="M78">
+        <v>21.3851587256304</v>
+      </c>
+      <c r="N78">
+        <v>27.42384127436959</v>
+      </c>
+      <c r="O78">
+        <v>8.775629207798271</v>
+      </c>
+      <c r="P78">
+        <v>18.64821206657132</v>
+      </c>
+      <c r="Q78">
+        <v>41.94821206657132</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2991221323553905</v>
+      </c>
+      <c r="T78">
+        <v>1.902423873097464</v>
+      </c>
+      <c r="U78">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V78">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W78">
+        <v>0.062152</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>2.282377261081618</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.118994177085525</v>
+      </c>
+      <c r="C79">
+        <v>77.27660297530949</v>
+      </c>
+      <c r="D79">
+        <v>314.3284891139627</v>
+      </c>
+      <c r="E79">
+        <v>236.9922937507919</v>
+      </c>
+      <c r="F79">
+        <v>237.0518861386533</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>307.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K79">
+        <v>23.3</v>
+      </c>
+      <c r="L79">
+        <v>48.809</v>
+      </c>
+      <c r="M79">
+        <v>21.66654239307291</v>
+      </c>
+      <c r="N79">
+        <v>27.14245760692709</v>
+      </c>
+      <c r="O79">
+        <v>8.68558643421667</v>
+      </c>
+      <c r="P79">
+        <v>18.45687117271042</v>
+      </c>
+      <c r="Q79">
+        <v>41.75687117271042</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.309291900371848</v>
+      </c>
+      <c r="T79">
+        <v>1.9767441365469</v>
+      </c>
+      <c r="U79">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V79">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W79">
+        <v>0.062152</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>2.252735997950689</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1189635224057564</v>
+      </c>
+      <c r="C80">
+        <v>74.28377645047539</v>
+      </c>
+      <c r="D80">
+        <v>314.4142585130073</v>
+      </c>
+      <c r="E80">
+        <v>240.0708896746706</v>
+      </c>
+      <c r="F80">
+        <v>240.1304820625319</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>307.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K80">
+        <v>23.3</v>
+      </c>
+      <c r="L80">
+        <v>48.809</v>
+      </c>
+      <c r="M80">
+        <v>21.94792606051542</v>
+      </c>
+      <c r="N80">
+        <v>26.86107393948458</v>
+      </c>
+      <c r="O80">
+        <v>8.595543660635068</v>
+      </c>
+      <c r="P80">
+        <v>18.26553027884951</v>
+      </c>
+      <c r="Q80">
+        <v>41.56553027884951</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.320386192753438</v>
+      </c>
+      <c r="T80">
+        <v>2.05782078758265</v>
+      </c>
+      <c r="U80">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V80">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W80">
+        <v>0.062152</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>2.22385476720773</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1189328677259877</v>
+      </c>
+      <c r="C81">
+        <v>71.29099674543599</v>
+      </c>
+      <c r="D81">
+        <v>314.5000747318465</v>
+      </c>
+      <c r="E81">
+        <v>243.1494855985492</v>
+      </c>
+      <c r="F81">
+        <v>243.2090779864105</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>307.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K81">
+        <v>23.3</v>
+      </c>
+      <c r="L81">
+        <v>48.809</v>
+      </c>
+      <c r="M81">
+        <v>22.22930972795792</v>
+      </c>
+      <c r="N81">
+        <v>26.57969027204208</v>
+      </c>
+      <c r="O81">
+        <v>8.505500887053465</v>
+      </c>
+      <c r="P81">
+        <v>18.07418938498861</v>
+      </c>
+      <c r="Q81">
+        <v>41.37418938498861</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3325370844094652</v>
+      </c>
+      <c r="T81">
+        <v>2.146619024431327</v>
+      </c>
+      <c r="U81">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V81">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W81">
+        <v>0.062152</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>2.195704706863329</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.118902213046219</v>
+      </c>
+      <c r="C82">
+        <v>68.29826389853886</v>
+      </c>
+      <c r="D82">
+        <v>314.585937808828</v>
+      </c>
+      <c r="E82">
+        <v>246.2280815224278</v>
+      </c>
+      <c r="F82">
+        <v>246.2876739102891</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>307.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K82">
+        <v>23.3</v>
+      </c>
+      <c r="L82">
+        <v>48.809</v>
+      </c>
+      <c r="M82">
+        <v>22.51069339540043</v>
+      </c>
+      <c r="N82">
+        <v>26.29830660459957</v>
+      </c>
+      <c r="O82">
+        <v>8.415458113471864</v>
+      </c>
+      <c r="P82">
+        <v>17.88284849112771</v>
+      </c>
+      <c r="Q82">
+        <v>41.18284849112771</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3459030652310949</v>
+      </c>
+      <c r="T82">
+        <v>2.244297084964872</v>
+      </c>
+      <c r="U82">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V82">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W82">
+        <v>0.062152</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>2.168258398027537</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1188715583664503</v>
+      </c>
+      <c r="C83">
+        <v>65.3055779481731</v>
+      </c>
+      <c r="D83">
+        <v>314.6718477823408</v>
+      </c>
+      <c r="E83">
+        <v>249.3066774463064</v>
+      </c>
+      <c r="F83">
+        <v>249.3662698341677</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>307.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K83">
+        <v>23.3</v>
+      </c>
+      <c r="L83">
+        <v>48.809</v>
+      </c>
+      <c r="M83">
+        <v>22.79207706284293</v>
+      </c>
+      <c r="N83">
+        <v>26.01692293715707</v>
+      </c>
+      <c r="O83">
+        <v>8.325415339890263</v>
+      </c>
+      <c r="P83">
+        <v>17.6915075972668</v>
+      </c>
+      <c r="Q83">
+        <v>40.9915075972668</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3606759914023701</v>
+      </c>
+      <c r="T83">
+        <v>2.352257046607213</v>
+      </c>
+      <c r="U83">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V83">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W83">
+        <v>0.062152</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>2.141489775829667</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1188409036866816</v>
+      </c>
+      <c r="C84">
+        <v>62.31293893277009</v>
+      </c>
+      <c r="D84">
+        <v>314.7578046908164</v>
+      </c>
+      <c r="E84">
+        <v>252.385273370185</v>
+      </c>
+      <c r="F84">
+        <v>252.4448657580463</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>307.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K84">
+        <v>23.3</v>
+      </c>
+      <c r="L84">
+        <v>48.809</v>
+      </c>
+      <c r="M84">
+        <v>23.07346073028544</v>
+      </c>
+      <c r="N84">
+        <v>25.73553926971456</v>
+      </c>
+      <c r="O84">
+        <v>8.23537256630866</v>
+      </c>
+      <c r="P84">
+        <v>17.5001667034059</v>
+      </c>
+      <c r="Q84">
+        <v>40.80016670340589</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.377090353814898</v>
+      </c>
+      <c r="T84">
+        <v>2.472212559543146</v>
+      </c>
+      <c r="U84">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V84">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W84">
+        <v>0.062152</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>2.115374046856134</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1188102490069129</v>
+      </c>
+      <c r="C85">
+        <v>59.32034689080319</v>
+      </c>
+      <c r="D85">
+        <v>314.8438085727282</v>
+      </c>
+      <c r="E85">
+        <v>255.4638692940636</v>
+      </c>
+      <c r="F85">
+        <v>255.523461681925</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>307.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K85">
+        <v>23.3</v>
+      </c>
+      <c r="L85">
+        <v>48.809</v>
+      </c>
+      <c r="M85">
+        <v>23.35484439772794</v>
+      </c>
+      <c r="N85">
+        <v>25.45415560227205</v>
+      </c>
+      <c r="O85">
+        <v>8.145329792727058</v>
+      </c>
+      <c r="P85">
+        <v>17.308825809545</v>
+      </c>
+      <c r="Q85">
+        <v>40.608825809545</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3954358176877233</v>
+      </c>
+      <c r="T85">
+        <v>2.606280485765659</v>
+      </c>
+      <c r="U85">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V85">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W85">
+        <v>0.062152</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>2.089887612556662</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1187795943271442</v>
+      </c>
+      <c r="C86">
+        <v>56.32780186078776</v>
+      </c>
+      <c r="D86">
+        <v>314.9298594665913</v>
+      </c>
+      <c r="E86">
+        <v>258.5424652179422</v>
+      </c>
+      <c r="F86">
+        <v>258.6020576058036</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>307.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K86">
+        <v>23.3</v>
+      </c>
+      <c r="L86">
+        <v>48.809</v>
+      </c>
+      <c r="M86">
+        <v>23.63622806517045</v>
+      </c>
+      <c r="N86">
+        <v>25.17277193482955</v>
+      </c>
+      <c r="O86">
+        <v>8.055287019145457</v>
+      </c>
+      <c r="P86">
+        <v>17.11748491568409</v>
+      </c>
+      <c r="Q86">
+        <v>40.41748491568409</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4160744645446515</v>
+      </c>
+      <c r="T86">
+        <v>2.757106902765985</v>
+      </c>
+      <c r="U86">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V86">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W86">
+        <v>0.062152</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>2.065007998121464</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1187489396473756</v>
+      </c>
+      <c r="C87">
+        <v>53.33530388128116</v>
+      </c>
+      <c r="D87">
+        <v>315.0159574109633</v>
+      </c>
+      <c r="E87">
+        <v>261.6210611418208</v>
+      </c>
+      <c r="F87">
+        <v>261.6806535296822</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>307.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K87">
+        <v>23.3</v>
+      </c>
+      <c r="L87">
+        <v>48.809</v>
+      </c>
+      <c r="M87">
+        <v>23.91761173261295</v>
+      </c>
+      <c r="N87">
+        <v>24.89138826738705</v>
+      </c>
+      <c r="O87">
+        <v>7.965244245563857</v>
+      </c>
+      <c r="P87">
+        <v>16.92614402182319</v>
+      </c>
+      <c r="Q87">
+        <v>40.22614402182319</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4394649309825037</v>
+      </c>
+      <c r="T87">
+        <v>2.92804350869969</v>
+      </c>
+      <c r="U87">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V87">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W87">
+        <v>0.062152</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>2.040713786378859</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1187182849676069</v>
+      </c>
+      <c r="C88">
+        <v>50.34285299088305</v>
+      </c>
+      <c r="D88">
+        <v>315.1021024444438</v>
+      </c>
+      <c r="E88">
+        <v>264.6996570656994</v>
+      </c>
+      <c r="F88">
+        <v>264.7592494535608</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>307.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K88">
+        <v>23.3</v>
+      </c>
+      <c r="L88">
+        <v>48.809</v>
+      </c>
+      <c r="M88">
+        <v>24.19899540005546</v>
+      </c>
+      <c r="N88">
+        <v>24.61000459994454</v>
+      </c>
+      <c r="O88">
+        <v>7.875201471982255</v>
+      </c>
+      <c r="P88">
+        <v>16.73480312796229</v>
+      </c>
+      <c r="Q88">
+        <v>40.03480312796229</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4661968926257634</v>
+      </c>
+      <c r="T88">
+        <v>3.123399629766781</v>
+      </c>
+      <c r="U88">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V88">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W88">
+        <v>0.062152</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>2.016984556304686</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1311703902878382</v>
+      </c>
+      <c r="C89">
+        <v>15.76147703713815</v>
+      </c>
+      <c r="D89">
+        <v>283.5993224145776</v>
+      </c>
+      <c r="E89">
+        <v>267.778252989578</v>
+      </c>
+      <c r="F89">
+        <v>267.8378453774394</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>307.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K89">
+        <v>23.3</v>
+      </c>
+      <c r="L89">
+        <v>48.809</v>
+      </c>
+      <c r="M89">
+        <v>30.13175760496193</v>
+      </c>
+      <c r="N89">
+        <v>18.67724239503806</v>
+      </c>
+      <c r="O89">
+        <v>5.976717566412182</v>
+      </c>
+      <c r="P89">
+        <v>12.70052482862588</v>
+      </c>
+      <c r="Q89">
+        <v>36.00052482862588</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4970414637526015</v>
+      </c>
+      <c r="T89">
+        <v>3.348810538690347</v>
+      </c>
+      <c r="U89">
+        <v>0.1125</v>
+      </c>
+      <c r="V89">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W89">
+        <v>0.0765</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>1.619852404227571</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1312832156080695</v>
+      </c>
+      <c r="C90">
+        <v>12.42621216793049</v>
+      </c>
+      <c r="D90">
+        <v>283.3426534692485</v>
+      </c>
+      <c r="E90">
+        <v>270.8568489134566</v>
+      </c>
+      <c r="F90">
+        <v>270.916441301318</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>307.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K90">
+        <v>23.3</v>
+      </c>
+      <c r="L90">
+        <v>48.809</v>
+      </c>
+      <c r="M90">
+        <v>30.47809964639828</v>
+      </c>
+      <c r="N90">
+        <v>18.33090035360172</v>
+      </c>
+      <c r="O90">
+        <v>5.865888113152551</v>
+      </c>
+      <c r="P90">
+        <v>12.46501224044917</v>
+      </c>
+      <c r="Q90">
+        <v>35.76501224044917</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5330267967339126</v>
+      </c>
+      <c r="T90">
+        <v>3.611789932434508</v>
+      </c>
+      <c r="U90">
+        <v>0.1125</v>
+      </c>
+      <c r="V90">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W90">
+        <v>0.0765</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>1.601444990543167</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1313960409283008</v>
+      </c>
+      <c r="C91">
+        <v>9.091411470341484</v>
+      </c>
+      <c r="D91">
+        <v>283.0864486955381</v>
+      </c>
+      <c r="E91">
+        <v>273.9354448373352</v>
+      </c>
+      <c r="F91">
+        <v>273.9950372251966</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>307.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K91">
+        <v>23.3</v>
+      </c>
+      <c r="L91">
+        <v>48.809</v>
+      </c>
+      <c r="M91">
+        <v>30.82444168783462</v>
+      </c>
+      <c r="N91">
+        <v>17.98455831216538</v>
+      </c>
+      <c r="O91">
+        <v>5.755058659892923</v>
+      </c>
+      <c r="P91">
+        <v>12.22949965227246</v>
+      </c>
+      <c r="Q91">
+        <v>35.52949965227246</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5755549175300076</v>
+      </c>
+      <c r="T91">
+        <v>3.92258376140488</v>
+      </c>
+      <c r="U91">
+        <v>0.1125</v>
+      </c>
+      <c r="V91">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W91">
+        <v>0.0765</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>1.58345122660448</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1315088662485321</v>
+      </c>
+      <c r="C92">
+        <v>5.757073686365686</v>
+      </c>
+      <c r="D92">
+        <v>282.8307068354409</v>
+      </c>
+      <c r="E92">
+        <v>277.0140407612139</v>
+      </c>
+      <c r="F92">
+        <v>277.0736331490752</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>307.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K92">
+        <v>23.3</v>
+      </c>
+      <c r="L92">
+        <v>48.809</v>
+      </c>
+      <c r="M92">
+        <v>31.17078372927097</v>
+      </c>
+      <c r="N92">
+        <v>17.63821627072903</v>
+      </c>
+      <c r="O92">
+        <v>5.644229206633291</v>
+      </c>
+      <c r="P92">
+        <v>11.99398706409574</v>
+      </c>
+      <c r="Q92">
+        <v>35.29398706409575</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6265886624853216</v>
+      </c>
+      <c r="T92">
+        <v>4.295536356169326</v>
+      </c>
+      <c r="U92">
+        <v>0.1125</v>
+      </c>
+      <c r="V92">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W92">
+        <v>0.0765</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>1.565857324086652</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1316216915687635</v>
+      </c>
+      <c r="C93">
+        <v>2.423197562539201</v>
+      </c>
+      <c r="D93">
+        <v>282.575426635493</v>
+      </c>
+      <c r="E93">
+        <v>280.0926366850925</v>
+      </c>
+      <c r="F93">
+        <v>280.1522290729538</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>307.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K93">
+        <v>23.3</v>
+      </c>
+      <c r="L93">
+        <v>48.809</v>
+      </c>
+      <c r="M93">
+        <v>31.51712577070731</v>
+      </c>
+      <c r="N93">
+        <v>17.29187422929269</v>
+      </c>
+      <c r="O93">
+        <v>5.533399753373661</v>
+      </c>
+      <c r="P93">
+        <v>11.75847447591903</v>
+      </c>
+      <c r="Q93">
+        <v>35.05847447591903</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6889632396529277</v>
+      </c>
+      <c r="T93">
+        <v>4.751367305325872</v>
+      </c>
+      <c r="U93">
+        <v>0.1125</v>
+      </c>
+      <c r="V93">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W93">
+        <v>0.0765</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>1.548650100745041</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1317345168889948</v>
+      </c>
+      <c r="C94">
+        <v>-0.9102181500803681</v>
+      </c>
+      <c r="D94">
+        <v>282.3206068467521</v>
+      </c>
+      <c r="E94">
+        <v>283.1712326089711</v>
+      </c>
+      <c r="F94">
+        <v>283.2308249968325</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>307.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K94">
+        <v>23.3</v>
+      </c>
+      <c r="L94">
+        <v>48.809</v>
+      </c>
+      <c r="M94">
+        <v>31.86346781214366</v>
+      </c>
+      <c r="N94">
+        <v>16.94553218785634</v>
+      </c>
+      <c r="O94">
+        <v>5.42257030011403</v>
+      </c>
+      <c r="P94">
+        <v>11.52296188774231</v>
+      </c>
+      <c r="Q94">
+        <v>34.82296188774231</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7669314611124352</v>
+      </c>
+      <c r="T94">
+        <v>5.321155991771555</v>
+      </c>
+      <c r="U94">
+        <v>0.1125</v>
+      </c>
+      <c r="V94">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W94">
+        <v>0.0765</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>1.531816947476073</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1318473422092261</v>
+      </c>
+      <c r="C95">
+        <v>-4.243174695934215</v>
+      </c>
+      <c r="D95">
+        <v>282.0662462247769</v>
+      </c>
+      <c r="E95">
+        <v>286.2498285328497</v>
+      </c>
+      <c r="F95">
+        <v>286.3094209207111</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>307.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K95">
+        <v>23.3</v>
+      </c>
+      <c r="L95">
+        <v>48.809</v>
+      </c>
+      <c r="M95">
+        <v>32.20980985358</v>
+      </c>
+      <c r="N95">
+        <v>16.59919014642</v>
+      </c>
+      <c r="O95">
+        <v>5.311740846854401</v>
+      </c>
+      <c r="P95">
+        <v>11.2874492995656</v>
+      </c>
+      <c r="Q95">
+        <v>34.5874492995656</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8671763172746589</v>
+      </c>
+      <c r="T95">
+        <v>6.053741445773146</v>
+      </c>
+      <c r="U95">
+        <v>0.1125</v>
+      </c>
+      <c r="V95">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W95">
+        <v>0.0765</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>1.515345797503212</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1976491170770281</v>
+      </c>
+      <c r="C96">
+        <v>-104.4821238422724</v>
+      </c>
+      <c r="D96">
+        <v>184.9058930023173</v>
+      </c>
+      <c r="E96">
+        <v>289.3284244567283</v>
+      </c>
+      <c r="F96">
+        <v>289.3880168445897</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>307.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K96">
+        <v>23.3</v>
+      </c>
+      <c r="L96">
+        <v>48.809</v>
+      </c>
+      <c r="M96">
+        <v>56.89368411164633</v>
+      </c>
+      <c r="N96">
+        <v>-8.084684111646332</v>
+      </c>
+      <c r="O96">
+        <v>-2.587098915726827</v>
+      </c>
+      <c r="P96">
+        <v>-5.497585195919505</v>
+      </c>
+      <c r="Q96">
+        <v>17.8024148040805</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.059648239623929</v>
+      </c>
+      <c r="T96">
+        <v>7.460318660953332</v>
+      </c>
+      <c r="U96">
+        <v>0.1966</v>
+      </c>
+      <c r="V96">
+        <v>0.2745274847969068</v>
+      </c>
+      <c r="W96">
+        <v>0.1426278964889281</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.8578983899903334</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1992271170770282</v>
+      </c>
+      <c r="C97">
+        <v>-109.0756245869762</v>
+      </c>
+      <c r="D97">
+        <v>183.3909881814921</v>
+      </c>
+      <c r="E97">
+        <v>292.407020380607</v>
+      </c>
+      <c r="F97">
+        <v>292.4666127684683</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>307.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K97">
+        <v>23.3</v>
+      </c>
+      <c r="L97">
+        <v>48.809</v>
+      </c>
+      <c r="M97">
+        <v>57.49893607028088</v>
+      </c>
+      <c r="N97">
+        <v>-8.689936070280879</v>
+      </c>
+      <c r="O97">
+        <v>-2.780779542489882</v>
+      </c>
+      <c r="P97">
+        <v>-5.909156527790998</v>
+      </c>
+      <c r="Q97">
+        <v>17.390843472209</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.263817887548716</v>
+      </c>
+      <c r="T97">
+        <v>8.952382393144006</v>
+      </c>
+      <c r="U97">
+        <v>0.1966</v>
+      </c>
+      <c r="V97">
+        <v>0.2716377217990445</v>
+      </c>
+      <c r="W97">
+        <v>0.1431960238943079</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.8488678806220139</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2008051170770281</v>
+      </c>
+      <c r="C98">
+        <v>-113.6445042953688</v>
+      </c>
+      <c r="D98">
+        <v>181.900704396978</v>
+      </c>
+      <c r="E98">
+        <v>295.4856163044855</v>
+      </c>
+      <c r="F98">
+        <v>295.5452086923469</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>307.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K98">
+        <v>23.3</v>
+      </c>
+      <c r="L98">
+        <v>48.809</v>
+      </c>
+      <c r="M98">
+        <v>58.1041880289154</v>
+      </c>
+      <c r="N98">
+        <v>-9.295188028915398</v>
+      </c>
+      <c r="O98">
+        <v>-2.974460169252928</v>
+      </c>
+      <c r="P98">
+        <v>-6.32072785966247</v>
+      </c>
+      <c r="Q98">
+        <v>16.97927214033753</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.570072359435891</v>
+      </c>
+      <c r="T98">
+        <v>11.19047799142998</v>
+      </c>
+      <c r="U98">
+        <v>0.1966</v>
+      </c>
+      <c r="V98">
+        <v>0.2688081621969712</v>
+      </c>
+      <c r="W98">
+        <v>0.1437523153120754</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.8400255068655349</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2023831170770282</v>
+      </c>
+      <c r="C99">
+        <v>-118.1893583603337</v>
+      </c>
+      <c r="D99">
+        <v>180.4344462558919</v>
+      </c>
+      <c r="E99">
+        <v>298.5642122283642</v>
+      </c>
+      <c r="F99">
+        <v>298.6238046162255</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>307.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K99">
+        <v>23.3</v>
+      </c>
+      <c r="L99">
+        <v>48.809</v>
+      </c>
+      <c r="M99">
+        <v>58.70943998754993</v>
+      </c>
+      <c r="N99">
+        <v>-9.900439987549937</v>
+      </c>
+      <c r="O99">
+        <v>-3.16814079601598</v>
+      </c>
+      <c r="P99">
+        <v>-6.732299191533957</v>
+      </c>
+      <c r="Q99">
+        <v>16.56770080846604</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.080496479247856</v>
+      </c>
+      <c r="T99">
+        <v>14.92063732190664</v>
+      </c>
+      <c r="U99">
+        <v>0.1966</v>
+      </c>
+      <c r="V99">
+        <v>0.2660369440299921</v>
+      </c>
+      <c r="W99">
+        <v>0.1442971368037035</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.8313654500937251</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2039611170770282</v>
+      </c>
+      <c r="C100">
+        <v>-122.7107631309812</v>
+      </c>
+      <c r="D100">
+        <v>178.9916374091229</v>
+      </c>
+      <c r="E100">
+        <v>301.6428081522428</v>
+      </c>
+      <c r="F100">
+        <v>301.7024005401041</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>307.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K100">
+        <v>23.3</v>
+      </c>
+      <c r="L100">
+        <v>48.809</v>
+      </c>
+      <c r="M100">
+        <v>59.31469194618447</v>
+      </c>
+      <c r="N100">
+        <v>-10.50569194618447</v>
+      </c>
+      <c r="O100">
+        <v>-3.361821422779031</v>
+      </c>
+      <c r="P100">
+        <v>-7.14387052340544</v>
+      </c>
+      <c r="Q100">
+        <v>16.15612947659456</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.101344718871784</v>
+      </c>
+      <c r="T100">
+        <v>22.38095598285996</v>
+      </c>
+      <c r="U100">
+        <v>0.1966</v>
+      </c>
+      <c r="V100">
+        <v>0.2633222813358085</v>
+      </c>
+      <c r="W100">
+        <v>0.1448308394893801</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.8228821291744015</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2055391170770282</v>
+      </c>
+      <c r="C101">
+        <v>-127.2092766680093</v>
+      </c>
+      <c r="D101">
+        <v>177.5717197959735</v>
+      </c>
+      <c r="E101">
+        <v>304.7214040761214</v>
+      </c>
+      <c r="F101">
+        <v>304.7809964639828</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>307.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>72.10899999999999</v>
+      </c>
+      <c r="K101">
+        <v>23.3</v>
+      </c>
+      <c r="L101">
+        <v>48.809</v>
+      </c>
+      <c r="M101">
+        <v>59.91994390481901</v>
+      </c>
+      <c r="N101">
+        <v>-11.11094390481902</v>
+      </c>
+      <c r="O101">
+        <v>-3.555502049542086</v>
+      </c>
+      <c r="P101">
+        <v>-7.55544185527693</v>
+      </c>
+      <c r="Q101">
+        <v>15.74455814472307</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.163889437743566</v>
+      </c>
+      <c r="T101">
+        <v>44.76191196571992</v>
+      </c>
+      <c r="U101">
+        <v>0.1966</v>
+      </c>
+      <c r="V101">
+        <v>0.2606624603122145</v>
+      </c>
+      <c r="W101">
+        <v>0.1453537603026186</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.81457018847567</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
